--- a/examples/STUDY01_TRAIL01/outputs/reports/ADAM_issues.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/ADAM_issues.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -83,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,7 +95,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -481,7 +489,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
@@ -615,7 +623,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
@@ -633,7 +641,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
@@ -708,7 +716,9 @@
           <t>EC end date (12Apr2022) is before start date (13Apr2022) for treatment: DRUG A 10MG at visit BASELINE</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -720,34 +730,36 @@
       <c r="J4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>ECCHK001</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>EC end date (25Mar2022) is before start date (28Mar2022) for treatment: DRUG A 10MG at visit BASELINE</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr"/>
-      <c r="H5" s="7" t="inlineStr"/>
-      <c r="I5" s="7" t="inlineStr"/>
-      <c r="J5" s="7" t="inlineStr"/>
+      <c r="E5" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -768,7 +780,9 @@
           <t>EC end date (01Feb2023) is before start date (02Feb2023) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -780,34 +794,36 @@
       <c r="J6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ECCHK001</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>SUBJ-006</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D7" s="7" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>EC end date (05Apr2022) is before start date (11Apr2022) for treatment: DRUG A 10MG at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
-      <c r="I7" s="7" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
+      <c r="E7" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -828,7 +844,9 @@
           <t>EC end date (28Apr2023) is before start date (02May2023) for treatment: DRUG A 10MG at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -840,34 +858,36 @@
       <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>ECCHK003</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Dose unit (ECDOSU) is missing although dose (ECDOSE=10) is present for treatment: PLACEBO at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E9" s="7" t="n"/>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr"/>
-      <c r="H9" s="7" t="inlineStr"/>
-      <c r="I9" s="7" t="inlineStr"/>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="E9" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr"/>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -888,7 +908,9 @@
           <t>Dose unit (ECDOSU) is missing although dose (ECDOSE=40) is present for treatment: DRUG A 10MG at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
+      <c r="E10" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -900,34 +922,36 @@
       <c r="J10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ECCHK003</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>SUBJ-008</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Dose unit (ECDOSU) is missing although dose (ECDOSE=20) is present for treatment: DRUG A 10MG at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr"/>
-      <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="7" t="inlineStr"/>
-      <c r="J11" s="7" t="inlineStr"/>
+      <c r="E11" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="8" t="inlineStr"/>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -945,10 +969,12 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.8 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -960,34 +986,36 @@
       <c r="J12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="n"/>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 10.8 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="8" t="inlineStr"/>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1008,7 +1036,9 @@
           <t>Alanine Aminotransf (ALT) = 57.25 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
+      <c r="E14" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1020,34 +1050,36 @@
       <c r="J14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Aspartate Aminotransf (AST) = 41.8 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr"/>
+      <c r="E15" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1068,7 +1100,9 @@
           <t>Creatinine (CREAT) = 119.23 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
+      <c r="E16" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1080,34 +1114,36 @@
       <c r="J16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 18.21 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E17" s="7" t="n"/>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="E17" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1128,7 +1164,9 @@
           <t>Platelets (PLT) = 403.3 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
+      <c r="E18" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1140,34 +1178,36 @@
       <c r="J18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E19" s="7" t="n"/>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr"/>
+      <c r="E19" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="8" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1185,10 +1225,12 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 11.11 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 38.05 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1200,34 +1242,36 @@
       <c r="J20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 38.05 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="n"/>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 11.37 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -1245,10 +1289,12 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 11.37 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 11.11 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1260,34 +1306,36 @@
       <c r="J22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 11.65 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
-      <c r="I23" s="7" t="inlineStr"/>
-      <c r="J23" s="7" t="inlineStr"/>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.76 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="8" t="inlineStr"/>
+      <c r="J23" s="8" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -1305,10 +1353,12 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.76 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.26 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1320,34 +1370,36 @@
       <c r="J24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 12.26 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="n"/>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
-      <c r="I25" s="7" t="inlineStr"/>
-      <c r="J25" s="7" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 11.65 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="8" t="inlineStr"/>
+      <c r="J25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -1368,7 +1420,9 @@
           <t>Hemoglobin (HGB) = 19.67 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
+      <c r="E26" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1380,34 +1434,36 @@
       <c r="J26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D27" s="8" t="inlineStr">
         <is>
           <t>Bilirubin (BILI) = 23.45 umol/L outside normal range [3.0 - 21.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E27" s="7" t="n"/>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr"/>
-      <c r="H27" s="7" t="inlineStr"/>
-      <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
+      <c r="E27" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="8" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -1425,10 +1481,12 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 18.49 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1440,34 +1498,36 @@
       <c r="J28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>SUBJ-002</t>
         </is>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr"/>
-      <c r="H29" s="7" t="inlineStr"/>
-      <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 18.49 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="8" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -1488,7 +1548,9 @@
           <t>Platelets (PLT) = 418.9 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
+      <c r="E30" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1500,34 +1562,36 @@
       <c r="J30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D31" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 121.44 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr"/>
-      <c r="H31" s="7" t="inlineStr"/>
-      <c r="I31" s="7" t="inlineStr"/>
-      <c r="J31" s="7" t="inlineStr"/>
+      <c r="E31" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr"/>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+      <c r="J31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -1548,7 +1612,9 @@
           <t>Hemoglobin (HGB) = 17.73 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E32" s="6" t="n"/>
+      <c r="E32" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1560,34 +1626,36 @@
       <c r="J32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 129.25 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr"/>
-      <c r="H33" s="7" t="inlineStr"/>
-      <c r="I33" s="7" t="inlineStr"/>
-      <c r="J33" s="7" t="inlineStr"/>
+      <c r="E33" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -1605,10 +1673,12 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 6.91 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 108.1 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1620,34 +1690,36 @@
       <c r="J34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D35" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 108.1 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr"/>
-      <c r="H35" s="7" t="inlineStr"/>
-      <c r="I35" s="7" t="inlineStr"/>
-      <c r="J35" s="7" t="inlineStr"/>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 6.91 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="8" t="inlineStr"/>
+      <c r="J35" s="8" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -1668,7 +1740,9 @@
           <t>Alanine Aminotransf (ALT) = 63.28 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E36" s="6" t="n"/>
+      <c r="E36" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1680,34 +1754,36 @@
       <c r="J36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 18.99 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
-      <c r="H37" s="7" t="inlineStr"/>
-      <c r="I37" s="7" t="inlineStr"/>
-      <c r="J37" s="7" t="inlineStr"/>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 3.74 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="8" t="inlineStr"/>
+      <c r="J37" s="8" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -1725,10 +1801,12 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 3.74 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 18.99 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1740,34 +1818,36 @@
       <c r="J38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D39" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin A1C (HBA1C) = 3.91 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr"/>
-      <c r="H39" s="7" t="inlineStr"/>
-      <c r="I39" s="7" t="inlineStr"/>
-      <c r="J39" s="7" t="inlineStr"/>
+      <c r="E39" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G39" s="8" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="8" t="inlineStr"/>
+      <c r="J39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -1785,10 +1865,12 @@
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 61.45 U/L outside normal range [7.0 - 56.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 9.9 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1800,34 +1882,36 @@
       <c r="J40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D41" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 43.08 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr"/>
-      <c r="H41" s="7" t="inlineStr"/>
-      <c r="I41" s="7" t="inlineStr"/>
-      <c r="J41" s="7" t="inlineStr"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 8.11 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E41" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr"/>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="8" t="inlineStr"/>
+      <c r="J41" s="8" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -1845,10 +1929,12 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 8.11 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 43.08 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1860,34 +1946,36 @@
       <c r="J42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 9.9 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G43" s="7" t="inlineStr"/>
-      <c r="H43" s="7" t="inlineStr"/>
-      <c r="I43" s="7" t="inlineStr"/>
-      <c r="J43" s="7" t="inlineStr"/>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 61.45 U/L outside normal range [7.0 - 56.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="8" t="inlineStr"/>
+      <c r="J43" s="8" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -1908,7 +1996,9 @@
           <t>Platelets (PLT) = 136.12 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E44" s="6" t="n"/>
+      <c r="E44" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1920,34 +2010,36 @@
       <c r="J44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D45" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 119.16 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E45" s="7" t="n"/>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
-      <c r="I45" s="7" t="inlineStr"/>
-      <c r="J45" s="7" t="inlineStr"/>
+      <c r="E45" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="8" t="inlineStr"/>
+      <c r="J45" s="8" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -1968,7 +2060,9 @@
           <t>Hemoglobin (HGB) = 18.04 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E46" s="6" t="n"/>
+      <c r="E46" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -1980,34 +2074,36 @@
       <c r="J46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 42.65 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="n"/>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr"/>
-      <c r="H47" s="7" t="inlineStr"/>
-      <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="7" t="inlineStr"/>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.76 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="8" t="inlineStr"/>
+      <c r="J47" s="8" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -2025,10 +2121,12 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 19.48 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 42.65 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2040,34 +2138,36 @@
       <c r="J48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.76 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="n"/>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr"/>
-      <c r="H49" s="7" t="inlineStr"/>
-      <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
+      <c r="D49" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 19.48 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E49" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F49" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G49" s="8" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="8" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -2088,7 +2188,9 @@
           <t>Platelets (PLT) = 425.06 10^9/L outside normal range [150.0 - 400.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E50" s="6" t="n"/>
+      <c r="E50" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2100,34 +2202,36 @@
       <c r="J50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 61.39 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="n"/>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
-      <c r="J51" s="7" t="inlineStr"/>
+      <c r="D51" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 107.13 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E51" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F51" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G51" s="8" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="8" t="inlineStr"/>
+      <c r="J51" s="8" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -2145,10 +2249,12 @@
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 107.13 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 61.39 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2160,34 +2266,36 @@
       <c r="J52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D53" s="7" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>White Blood Cells (WBC) = 3.68 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E53" s="7" t="n"/>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr"/>
-      <c r="H53" s="7" t="inlineStr"/>
-      <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="7" t="inlineStr"/>
+      <c r="E53" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="8" t="inlineStr"/>
+      <c r="J53" s="8" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -2205,10 +2313,12 @@
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 20.08 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 7.37 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2220,34 +2330,36 @@
       <c r="J54" s="6" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.37 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="n"/>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr"/>
-      <c r="H55" s="7" t="inlineStr"/>
-      <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="7" t="inlineStr"/>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 20.08 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G55" s="8" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="8" t="inlineStr"/>
+      <c r="J55" s="8" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -2265,10 +2377,12 @@
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 111.97 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 7.0 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2280,34 +2394,36 @@
       <c r="J56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>SUBJ-004</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D57" s="7" t="inlineStr">
+      <c r="D57" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 3.36 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E57" s="7" t="n"/>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
-      <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
+      <c r="E57" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F57" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G57" s="8" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="8" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -2325,10 +2441,12 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.0 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E58" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 111.97 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2340,34 +2458,36 @@
       <c r="J58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D59" s="7" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin A1C (HBA1C) = 2.1 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E59" s="7" t="n"/>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
-      <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="7" t="inlineStr"/>
+      <c r="E59" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="8" t="inlineStr"/>
+      <c r="J59" s="8" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -2385,10 +2505,12 @@
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 59.75 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.53 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2400,34 +2522,36 @@
       <c r="J60" s="6" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 19.25 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="n"/>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="inlineStr"/>
-      <c r="H61" s="7" t="inlineStr"/>
-      <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="7" t="inlineStr"/>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 59.75 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F61" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="8" t="inlineStr"/>
+      <c r="J61" s="8" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -2445,10 +2569,12 @@
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.53 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 19.25 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2460,34 +2586,36 @@
       <c r="J62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D63" s="7" t="inlineStr">
+      <c r="D63" s="8" t="inlineStr">
         <is>
           <t>Alanine Aminotransf (ALT) = 61.75 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E63" s="7" t="n"/>
-      <c r="F63" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G63" s="7" t="inlineStr"/>
-      <c r="H63" s="7" t="inlineStr"/>
-      <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
+      <c r="E63" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F63" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G63" s="8" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="8" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -2505,10 +2633,12 @@
       </c>
       <c r="D64" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.41 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 18.42 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2520,34 +2650,36 @@
       <c r="J64" s="6" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 18.42 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E65" s="7" t="n"/>
-      <c r="F65" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G65" s="7" t="inlineStr"/>
-      <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="7" t="inlineStr"/>
-      <c r="J65" s="7" t="inlineStr"/>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>C-Reactive Protein (CRPROT) = 10.41 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G65" s="8" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="8" t="inlineStr"/>
+      <c r="J65" s="8" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -2565,10 +2697,12 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 60.6 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.81 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2580,34 +2714,36 @@
       <c r="J66" s="6" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C67" s="7" t="n">
+      <c r="C67" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>C-Reactive Protein (CRPROT) = 10.08 mg/L outside normal range [0.0 - 10.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E67" s="7" t="n"/>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
-      <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="7" t="inlineStr"/>
+      <c r="D67" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.88 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G67" s="8" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="8" t="inlineStr"/>
+      <c r="J67" s="8" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -2628,7 +2764,9 @@
           <t>Creatinine (CREAT) = 120.03 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E68" s="6" t="n"/>
+      <c r="E68" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2640,34 +2778,36 @@
       <c r="J68" s="6" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C69" s="7" t="n">
+      <c r="C69" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 3.88 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="n"/>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G69" s="7" t="inlineStr"/>
-      <c r="H69" s="7" t="inlineStr"/>
-      <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr"/>
+      <c r="D69" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 60.6 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G69" s="8" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="8" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -2685,10 +2825,12 @@
       </c>
       <c r="D70" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.81 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="n"/>
+          <t>Platelets (PLT) = 420.85 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2700,34 +2842,36 @@
       <c r="J70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C71" s="7" t="n">
+      <c r="C71" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 420.85 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="n"/>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G71" s="7" t="inlineStr"/>
-      <c r="H71" s="7" t="inlineStr"/>
-      <c r="I71" s="7" t="inlineStr"/>
-      <c r="J71" s="7" t="inlineStr"/>
+      <c r="D71" s="8" t="inlineStr">
+        <is>
+          <t>C-Reactive Protein (CRPROT) = 10.08 mg/L outside normal range [0.0 - 10.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E71" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G71" s="8" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="8" t="inlineStr"/>
+      <c r="J71" s="8" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -2745,10 +2889,12 @@
       </c>
       <c r="D72" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.76 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.84 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2760,34 +2906,36 @@
       <c r="J72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C73" s="7" t="n">
+      <c r="C73" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 8.91 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E73" s="7" t="n"/>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G73" s="7" t="inlineStr"/>
-      <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="7" t="inlineStr"/>
-      <c r="J73" s="7" t="inlineStr"/>
+      <c r="E73" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G73" s="8" t="inlineStr"/>
+      <c r="H73" s="8" t="inlineStr"/>
+      <c r="I73" s="8" t="inlineStr"/>
+      <c r="J73" s="8" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="6" t="inlineStr">
@@ -2808,7 +2956,9 @@
           <t>Hemoglobin (HGB) = 18.7 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E74" s="6" t="n"/>
+      <c r="E74" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2820,34 +2970,36 @@
       <c r="J74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
         <is>
           <t>SUBJ-005</t>
         </is>
       </c>
-      <c r="C75" s="7" t="n">
+      <c r="C75" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.84 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="n"/>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G75" s="7" t="inlineStr"/>
-      <c r="H75" s="7" t="inlineStr"/>
-      <c r="I75" s="7" t="inlineStr"/>
-      <c r="J75" s="7" t="inlineStr"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>C-Reactive Protein (CRPROT) = 10.76 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E75" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F75" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G75" s="8" t="inlineStr"/>
+      <c r="H75" s="8" t="inlineStr"/>
+      <c r="I75" s="8" t="inlineStr"/>
+      <c r="J75" s="8" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -2868,7 +3020,9 @@
           <t>Hemoglobin (HGB) = 10.77 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E76" s="6" t="n"/>
+      <c r="E76" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2880,34 +3034,36 @@
       <c r="J76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>SUBJ-006</t>
         </is>
       </c>
-      <c r="C77" s="7" t="n">
+      <c r="C77" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D77" s="7" t="inlineStr">
+      <c r="D77" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin A1C (HBA1C) = 7.42 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E77" s="7" t="n"/>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G77" s="7" t="inlineStr"/>
-      <c r="H77" s="7" t="inlineStr"/>
-      <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
+      <c r="E77" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F77" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G77" s="8" t="inlineStr"/>
+      <c r="H77" s="8" t="inlineStr"/>
+      <c r="I77" s="8" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
@@ -2928,7 +3084,9 @@
           <t>Platelets (PLT) = 452.85 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E78" s="6" t="n"/>
+      <c r="E78" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -2940,34 +3098,36 @@
       <c r="J78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>SUBJ-006</t>
         </is>
       </c>
-      <c r="C79" s="7" t="n">
+      <c r="C79" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 40.24 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="n"/>
-      <c r="F79" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
-      <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
+      <c r="D79" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.53 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E79" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F79" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G79" s="8" t="inlineStr"/>
+      <c r="H79" s="8" t="inlineStr"/>
+      <c r="I79" s="8" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
@@ -2985,10 +3145,12 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.53 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 40.24 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3000,34 +3162,36 @@
       <c r="J80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>SUBJ-006</t>
         </is>
       </c>
-      <c r="C81" s="7" t="n">
+      <c r="C81" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D81" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 418.86 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="n"/>
-      <c r="F81" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G81" s="7" t="inlineStr"/>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
+      <c r="D81" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 12.59 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F81" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G81" s="8" t="inlineStr"/>
+      <c r="H81" s="8" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr"/>
+      <c r="J81" s="8" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
@@ -3045,10 +3209,12 @@
       </c>
       <c r="D82" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.59 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E82" s="6" t="n"/>
+          <t>Platelets (PLT) = 418.86 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3060,34 +3226,36 @@
       <c r="J82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>Bilirubin (BILI) = 21.21 umol/L outside normal range [3.0 - 21.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="n"/>
-      <c r="F83" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="7" t="inlineStr"/>
+      <c r="D83" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 8.76 mmol/L outside normal range [3.9 - 7.8] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E83" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G83" s="8" t="inlineStr"/>
+      <c r="H83" s="8" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr"/>
+      <c r="J83" s="8" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
@@ -3108,7 +3276,9 @@
           <t>Creatinine (CREAT) = 114.67 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E84" s="6" t="n"/>
+      <c r="E84" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3120,34 +3290,36 @@
       <c r="J84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C85" s="7" t="n">
+      <c r="C85" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 8.76 mmol/L outside normal range [3.9 - 7.8] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E85" s="7" t="n"/>
-      <c r="F85" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G85" s="7" t="inlineStr"/>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
+      <c r="D85" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 18.17 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G85" s="8" t="inlineStr"/>
+      <c r="H85" s="8" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr"/>
+      <c r="J85" s="8" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
@@ -3165,10 +3337,12 @@
       </c>
       <c r="D86" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 18.17 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E86" s="6" t="n"/>
+          <t>Bilirubin (BILI) = 21.21 umol/L outside normal range [3.0 - 21.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3180,34 +3354,36 @@
       <c r="J86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C87" s="7" t="n">
+      <c r="C87" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D87" s="7" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 119.07 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E87" s="7" t="n"/>
-      <c r="F87" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
+      <c r="E87" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G87" s="8" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr"/>
+      <c r="I87" s="8" t="inlineStr"/>
+      <c r="J87" s="8" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
@@ -3225,10 +3401,12 @@
       </c>
       <c r="D88" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 18.53 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.56 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3240,34 +3418,36 @@
       <c r="J88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C89" s="7" t="n">
+      <c r="C89" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D89" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 12.56 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="n"/>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="inlineStr"/>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
+      <c r="D89" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 18.53 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E89" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F89" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G89" s="8" t="inlineStr"/>
+      <c r="H89" s="8" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr"/>
+      <c r="J89" s="8" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
@@ -3285,10 +3465,12 @@
       </c>
       <c r="D90" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 6.95 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="n"/>
+          <t>Glucose (GLUC) = 3.4 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3300,34 +3482,36 @@
       <c r="J90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C91" s="7" t="n">
+      <c r="C91" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D91" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 42.93 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="n"/>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="7" t="inlineStr"/>
-      <c r="J91" s="7" t="inlineStr"/>
+      <c r="D91" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 6.95 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F91" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G91" s="8" t="inlineStr"/>
+      <c r="H91" s="8" t="inlineStr"/>
+      <c r="I91" s="8" t="inlineStr"/>
+      <c r="J91" s="8" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
@@ -3345,10 +3529,12 @@
       </c>
       <c r="D92" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 3.4 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E92" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 42.93 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3360,34 +3546,36 @@
       <c r="J92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C93" s="7" t="n">
+      <c r="C93" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D93" s="7" t="inlineStr">
+      <c r="D93" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 18.09 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E93" s="7" t="n"/>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="7" t="inlineStr"/>
+      <c r="E93" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F93" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G93" s="8" t="inlineStr"/>
+      <c r="H93" s="8" t="inlineStr"/>
+      <c r="I93" s="8" t="inlineStr"/>
+      <c r="J93" s="8" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -3408,7 +3596,9 @@
           <t>Alanine Aminotransf (ALT) = 58.25 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E94" s="6" t="n"/>
+      <c r="E94" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3420,34 +3610,36 @@
       <c r="J94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C95" s="7" t="n">
+      <c r="C95" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D95" s="8" t="inlineStr">
         <is>
           <t>Aspartate Aminotransf (AST) = 42.3 U/L outside normal range [10.0 - 40.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E95" s="7" t="n"/>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="7" t="inlineStr"/>
-      <c r="J95" s="7" t="inlineStr"/>
+      <c r="E95" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F95" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G95" s="8" t="inlineStr"/>
+      <c r="H95" s="8" t="inlineStr"/>
+      <c r="I95" s="8" t="inlineStr"/>
+      <c r="J95" s="8" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
@@ -3465,10 +3657,12 @@
       </c>
       <c r="D96" s="6" t="inlineStr">
         <is>
-          <t>Bilirubin (BILI) = 22.61 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 11.95 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F96" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3480,34 +3674,36 @@
       <c r="J96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C97" s="7" t="n">
+      <c r="C97" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D97" s="7" t="inlineStr">
+      <c r="D97" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 447.19 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E97" s="7" t="n"/>
-      <c r="F97" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="7" t="inlineStr"/>
-      <c r="J97" s="7" t="inlineStr"/>
+      <c r="E97" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F97" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G97" s="8" t="inlineStr"/>
+      <c r="H97" s="8" t="inlineStr"/>
+      <c r="I97" s="8" t="inlineStr"/>
+      <c r="J97" s="8" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
@@ -3525,10 +3721,12 @@
       </c>
       <c r="D98" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 11.95 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E98" s="6" t="n"/>
+          <t>Bilirubin (BILI) = 22.61 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3540,34 +3738,36 @@
       <c r="J98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>SUBJ-007</t>
         </is>
       </c>
-      <c r="C99" s="7" t="n">
+      <c r="C99" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D99" s="7" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 3.76 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E99" s="7" t="n"/>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
+      <c r="E99" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F99" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G99" s="8" t="inlineStr"/>
+      <c r="H99" s="8" t="inlineStr"/>
+      <c r="I99" s="8" t="inlineStr"/>
+      <c r="J99" s="8" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
@@ -3588,7 +3788,9 @@
           <t>Platelets (PLT) = 428.48 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E100" s="6" t="n"/>
+      <c r="E100" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3600,34 +3802,36 @@
       <c r="J100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>SUBJ-008</t>
         </is>
       </c>
-      <c r="C101" s="7" t="n">
+      <c r="C101" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D101" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 8.75 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E101" s="7" t="n"/>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="7" t="inlineStr"/>
-      <c r="J101" s="7" t="inlineStr"/>
+      <c r="D101" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 117.19 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E101" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F101" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G101" s="8" t="inlineStr"/>
+      <c r="H101" s="8" t="inlineStr"/>
+      <c r="I101" s="8" t="inlineStr"/>
+      <c r="J101" s="8" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
@@ -3645,10 +3849,12 @@
       </c>
       <c r="D102" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 117.19 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 8.75 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3660,34 +3866,36 @@
       <c r="J102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
         <is>
           <t>SUBJ-008</t>
         </is>
       </c>
-      <c r="C103" s="7" t="n">
+      <c r="C103" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D103" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 61.07 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="n"/>
-      <c r="F103" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="7" t="inlineStr"/>
-      <c r="J103" s="7" t="inlineStr"/>
+      <c r="D103" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 8.59 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E103" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F103" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G103" s="8" t="inlineStr"/>
+      <c r="H103" s="8" t="inlineStr"/>
+      <c r="I103" s="8" t="inlineStr"/>
+      <c r="J103" s="8" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
@@ -3705,10 +3913,12 @@
       </c>
       <c r="D104" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 8.59 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 61.07 U/L outside normal range [7.0 - 56.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3720,34 +3930,36 @@
       <c r="J104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
         <is>
           <t>SUBJ-008</t>
         </is>
       </c>
-      <c r="C105" s="7" t="n">
+      <c r="C105" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D105" s="7" t="inlineStr">
+      <c r="D105" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 421.13 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E105" s="7" t="n"/>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
-      <c r="I105" s="7" t="inlineStr"/>
-      <c r="J105" s="7" t="inlineStr"/>
+      <c r="E105" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F105" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G105" s="8" t="inlineStr"/>
+      <c r="H105" s="8" t="inlineStr"/>
+      <c r="I105" s="8" t="inlineStr"/>
+      <c r="J105" s="8" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
@@ -3768,7 +3980,9 @@
           <t>Hemoglobin (HGB) = 10.52 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E106" s="6" t="n"/>
+      <c r="E106" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3780,34 +3994,36 @@
       <c r="J106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="inlineStr">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
         <is>
           <t>SUBJ-009</t>
         </is>
       </c>
-      <c r="C107" s="7" t="n">
+      <c r="C107" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D107" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 40.95 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E107" s="7" t="n"/>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr"/>
-      <c r="H107" s="7" t="inlineStr"/>
-      <c r="I107" s="7" t="inlineStr"/>
-      <c r="J107" s="7" t="inlineStr"/>
+      <c r="D107" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 107.54 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E107" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F107" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G107" s="8" t="inlineStr"/>
+      <c r="H107" s="8" t="inlineStr"/>
+      <c r="I107" s="8" t="inlineStr"/>
+      <c r="J107" s="8" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
@@ -3825,10 +4041,12 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 107.54 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 40.95 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3840,34 +4058,36 @@
       <c r="J108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
         <is>
           <t>SUBJ-009</t>
         </is>
       </c>
-      <c r="C109" s="7" t="n">
+      <c r="C109" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D109" s="7" t="inlineStr">
-        <is>
-          <t>Bilirubin (BILI) = 2.6 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="n"/>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr"/>
-      <c r="I109" s="7" t="inlineStr"/>
-      <c r="J109" s="7" t="inlineStr"/>
+      <c r="D109" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 7.28 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F109" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G109" s="8" t="inlineStr"/>
+      <c r="H109" s="8" t="inlineStr"/>
+      <c r="I109" s="8" t="inlineStr"/>
+      <c r="J109" s="8" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
@@ -3888,7 +4108,9 @@
           <t>Glucose (GLUC) = 8.51 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E110" s="6" t="n"/>
+      <c r="E110" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3900,34 +4122,36 @@
       <c r="J110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
         <is>
           <t>SUBJ-009</t>
         </is>
       </c>
-      <c r="C111" s="7" t="n">
+      <c r="C111" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D111" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.28 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E111" s="7" t="n"/>
-      <c r="F111" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G111" s="7" t="inlineStr"/>
-      <c r="H111" s="7" t="inlineStr"/>
-      <c r="I111" s="7" t="inlineStr"/>
-      <c r="J111" s="7" t="inlineStr"/>
+      <c r="D111" s="8" t="inlineStr">
+        <is>
+          <t>Bilirubin (BILI) = 2.6 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E111" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F111" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G111" s="8" t="inlineStr"/>
+      <c r="H111" s="8" t="inlineStr"/>
+      <c r="I111" s="8" t="inlineStr"/>
+      <c r="J111" s="8" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
@@ -3945,10 +4169,12 @@
       </c>
       <c r="D112" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.21 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.0 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -3960,34 +4186,36 @@
       <c r="J112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
         <is>
           <t>SUBJ-009</t>
         </is>
       </c>
-      <c r="C113" s="7" t="n">
+      <c r="C113" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D113" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 429.88 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E113" s="7" t="n"/>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr"/>
-      <c r="H113" s="7" t="inlineStr"/>
-      <c r="I113" s="7" t="inlineStr"/>
-      <c r="J113" s="7" t="inlineStr"/>
+      <c r="D113" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 10.21 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E113" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F113" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G113" s="8" t="inlineStr"/>
+      <c r="H113" s="8" t="inlineStr"/>
+      <c r="I113" s="8" t="inlineStr"/>
+      <c r="J113" s="8" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
@@ -4005,10 +4233,12 @@
       </c>
       <c r="D114" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.0 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="n"/>
+          <t>Platelets (PLT) = 429.88 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4020,34 +4250,36 @@
       <c r="J114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C115" s="7" t="n">
+      <c r="C115" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D115" s="7" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 3.83 mmol/L outside normal range [3.9 - 7.8] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E115" s="7" t="n"/>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
-      <c r="I115" s="7" t="inlineStr"/>
-      <c r="J115" s="7" t="inlineStr"/>
+      <c r="E115" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F115" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G115" s="8" t="inlineStr"/>
+      <c r="H115" s="8" t="inlineStr"/>
+      <c r="I115" s="8" t="inlineStr"/>
+      <c r="J115" s="8" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -4068,7 +4300,9 @@
           <t>Hemoglobin (HGB) = 11.09 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E116" s="6" t="n"/>
+      <c r="E116" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4080,34 +4314,36 @@
       <c r="J116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C117" s="7" t="n">
+      <c r="C117" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D117" s="7" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 409.42 10^9/L outside normal range [150.0 - 400.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E117" s="7" t="n"/>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr"/>
-      <c r="H117" s="7" t="inlineStr"/>
-      <c r="I117" s="7" t="inlineStr"/>
-      <c r="J117" s="7" t="inlineStr"/>
+      <c r="E117" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F117" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G117" s="8" t="inlineStr"/>
+      <c r="H117" s="8" t="inlineStr"/>
+      <c r="I117" s="8" t="inlineStr"/>
+      <c r="J117" s="8" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
@@ -4125,10 +4361,12 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 3.72 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.86 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4140,34 +4378,36 @@
       <c r="J118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C119" s="7" t="n">
+      <c r="C119" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D119" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.86 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E119" s="7" t="n"/>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr"/>
-      <c r="H119" s="7" t="inlineStr"/>
-      <c r="I119" s="7" t="inlineStr"/>
-      <c r="J119" s="7" t="inlineStr"/>
+      <c r="D119" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.72 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E119" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F119" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G119" s="8" t="inlineStr"/>
+      <c r="H119" s="8" t="inlineStr"/>
+      <c r="I119" s="8" t="inlineStr"/>
+      <c r="J119" s="8" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
@@ -4188,7 +4428,9 @@
           <t>White Blood Cells (WBC) = 3.77 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E120" s="6" t="n"/>
+      <c r="E120" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4200,34 +4442,36 @@
       <c r="J120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C121" s="7" t="n">
+      <c r="C121" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D121" s="7" t="inlineStr">
-        <is>
-          <t>C-Reactive Protein (CRPROT) = 11.21 mg/L outside normal range [0.0 - 10.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E121" s="7" t="n"/>
-      <c r="F121" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="inlineStr"/>
-      <c r="H121" s="7" t="inlineStr"/>
-      <c r="I121" s="7" t="inlineStr"/>
-      <c r="J121" s="7" t="inlineStr"/>
+      <c r="D121" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.8 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E121" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F121" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G121" s="8" t="inlineStr"/>
+      <c r="H121" s="8" t="inlineStr"/>
+      <c r="I121" s="8" t="inlineStr"/>
+      <c r="J121" s="8" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
@@ -4245,10 +4489,12 @@
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 3.8 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.22 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F122" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4260,34 +4506,36 @@
       <c r="J122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C123" s="7" t="n">
+      <c r="C123" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D123" s="7" t="inlineStr">
+      <c r="D123" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 11.46 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E123" s="7" t="n"/>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr"/>
-      <c r="H123" s="7" t="inlineStr"/>
-      <c r="I123" s="7" t="inlineStr"/>
-      <c r="J123" s="7" t="inlineStr"/>
+      <c r="E123" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F123" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G123" s="8" t="inlineStr"/>
+      <c r="H123" s="8" t="inlineStr"/>
+      <c r="I123" s="8" t="inlineStr"/>
+      <c r="J123" s="8" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
@@ -4305,10 +4553,12 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.22 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 11.21 mg/L outside normal range [0.0 - 10.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4320,34 +4570,36 @@
       <c r="J124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
         <is>
           <t>SUBJ-010</t>
         </is>
       </c>
-      <c r="C125" s="7" t="n">
+      <c r="C125" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D125" s="7" t="inlineStr">
-        <is>
-          <t>C-Reactive Protein (CRPROT) = 10.37 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="n"/>
-      <c r="F125" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="inlineStr"/>
-      <c r="H125" s="7" t="inlineStr"/>
-      <c r="I125" s="7" t="inlineStr"/>
-      <c r="J125" s="7" t="inlineStr"/>
+      <c r="D125" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 17.55 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E125" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F125" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G125" s="8" t="inlineStr"/>
+      <c r="H125" s="8" t="inlineStr"/>
+      <c r="I125" s="8" t="inlineStr"/>
+      <c r="J125" s="8" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
@@ -4365,10 +4617,12 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 17.55 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 10.37 mg/L outside normal range [0.0 - 10.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F126" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4380,34 +4634,36 @@
       <c r="J126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C127" s="7" t="n">
+      <c r="C127" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D127" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 17.75 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E127" s="7" t="n"/>
-      <c r="F127" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="inlineStr"/>
-      <c r="H127" s="7" t="inlineStr"/>
-      <c r="I127" s="7" t="inlineStr"/>
-      <c r="J127" s="7" t="inlineStr"/>
+      <c r="D127" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 7.29 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E127" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F127" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G127" s="8" t="inlineStr"/>
+      <c r="H127" s="8" t="inlineStr"/>
+      <c r="I127" s="8" t="inlineStr"/>
+      <c r="J127" s="8" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
@@ -4425,10 +4681,12 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.29 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.63 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4440,34 +4698,36 @@
       <c r="J128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B129" s="7" t="inlineStr">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C129" s="7" t="n">
+      <c r="C129" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D129" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 437.52 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E129" s="7" t="n"/>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr"/>
-      <c r="H129" s="7" t="inlineStr"/>
-      <c r="I129" s="7" t="inlineStr"/>
-      <c r="J129" s="7" t="inlineStr"/>
+      <c r="D129" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 17.75 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E129" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F129" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G129" s="8" t="inlineStr"/>
+      <c r="H129" s="8" t="inlineStr"/>
+      <c r="I129" s="8" t="inlineStr"/>
+      <c r="J129" s="8" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
@@ -4485,10 +4745,12 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.63 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="n"/>
+          <t>Platelets (PLT) = 437.52 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F130" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4500,34 +4762,36 @@
       <c r="J130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B131" s="7" t="inlineStr">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C131" s="7" t="n">
+      <c r="C131" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D131" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 8.75 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E131" s="7" t="n"/>
-      <c r="F131" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="inlineStr"/>
-      <c r="H131" s="7" t="inlineStr"/>
-      <c r="I131" s="7" t="inlineStr"/>
-      <c r="J131" s="7" t="inlineStr"/>
+      <c r="D131" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.82 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F131" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G131" s="8" t="inlineStr"/>
+      <c r="H131" s="8" t="inlineStr"/>
+      <c r="I131" s="8" t="inlineStr"/>
+      <c r="J131" s="8" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
@@ -4545,10 +4809,12 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.82 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="n"/>
+          <t>Glucose (GLUC) = 8.75 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F132" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4560,34 +4826,36 @@
       <c r="J132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B133" s="7" t="inlineStr">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C133" s="7" t="n">
+      <c r="C133" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D133" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 11.11 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E133" s="7" t="n"/>
-      <c r="F133" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="inlineStr"/>
-      <c r="H133" s="7" t="inlineStr"/>
-      <c r="I133" s="7" t="inlineStr"/>
-      <c r="J133" s="7" t="inlineStr"/>
+      <c r="D133" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.84 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E133" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F133" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G133" s="8" t="inlineStr"/>
+      <c r="H133" s="8" t="inlineStr"/>
+      <c r="I133" s="8" t="inlineStr"/>
+      <c r="J133" s="8" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
@@ -4605,10 +4873,12 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.84 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 11.11 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F134" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4620,34 +4890,36 @@
       <c r="J134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B135" s="7" t="inlineStr">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C135" s="7" t="n">
+      <c r="C135" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D135" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 60.75 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E135" s="7" t="n"/>
-      <c r="F135" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="inlineStr"/>
-      <c r="H135" s="7" t="inlineStr"/>
-      <c r="I135" s="7" t="inlineStr"/>
-      <c r="J135" s="7" t="inlineStr"/>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.68 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E135" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F135" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G135" s="8" t="inlineStr"/>
+      <c r="H135" s="8" t="inlineStr"/>
+      <c r="I135" s="8" t="inlineStr"/>
+      <c r="J135" s="8" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
@@ -4665,10 +4937,12 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 107.0 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="n"/>
+          <t>Glucose (GLUC) = 3.66 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4680,34 +4954,36 @@
       <c r="J136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B137" s="7" t="inlineStr">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C137" s="7" t="n">
+      <c r="C137" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D137" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 3.66 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E137" s="7" t="n"/>
-      <c r="F137" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="inlineStr"/>
-      <c r="H137" s="7" t="inlineStr"/>
-      <c r="I137" s="7" t="inlineStr"/>
-      <c r="J137" s="7" t="inlineStr"/>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 107.0 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F137" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G137" s="8" t="inlineStr"/>
+      <c r="H137" s="8" t="inlineStr"/>
+      <c r="I137" s="8" t="inlineStr"/>
+      <c r="J137" s="8" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -4725,10 +5001,12 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 19.18 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 60.75 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4740,34 +5018,36 @@
       <c r="J138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B139" s="7" t="inlineStr">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C139" s="7" t="n">
+      <c r="C139" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D139" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.68 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="n"/>
-      <c r="F139" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G139" s="7" t="inlineStr"/>
-      <c r="H139" s="7" t="inlineStr"/>
-      <c r="I139" s="7" t="inlineStr"/>
-      <c r="J139" s="7" t="inlineStr"/>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 19.18 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E139" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F139" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G139" s="8" t="inlineStr"/>
+      <c r="H139" s="8" t="inlineStr"/>
+      <c r="I139" s="8" t="inlineStr"/>
+      <c r="J139" s="8" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
@@ -4788,7 +5068,9 @@
           <t>Platelets (PLT) = 440.81 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E140" s="6" t="n"/>
+      <c r="E140" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4800,34 +5082,36 @@
       <c r="J140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B141" s="7" t="inlineStr">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C141" s="7" t="n">
+      <c r="C141" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D141" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 57.55 U/L outside normal range [7.0 - 56.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E141" s="7" t="n"/>
-      <c r="F141" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G141" s="7" t="inlineStr"/>
-      <c r="H141" s="7" t="inlineStr"/>
-      <c r="I141" s="7" t="inlineStr"/>
-      <c r="J141" s="7" t="inlineStr"/>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 7.1 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E141" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F141" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G141" s="8" t="inlineStr"/>
+      <c r="H141" s="8" t="inlineStr"/>
+      <c r="I141" s="8" t="inlineStr"/>
+      <c r="J141" s="8" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
@@ -4848,7 +5132,9 @@
           <t>Glucose (GLUC) = 8.31 mmol/L outside normal range [3.9 - 7.8] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E142" s="6" t="n"/>
+      <c r="E142" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F142" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4860,34 +5146,36 @@
       <c r="J142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B143" s="7" t="inlineStr">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="inlineStr">
         <is>
           <t>SUBJ-011</t>
         </is>
       </c>
-      <c r="C143" s="7" t="n">
+      <c r="C143" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D143" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 18.09 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E143" s="7" t="n"/>
-      <c r="F143" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="inlineStr"/>
-      <c r="H143" s="7" t="inlineStr"/>
-      <c r="I143" s="7" t="inlineStr"/>
-      <c r="J143" s="7" t="inlineStr"/>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 57.55 U/L outside normal range [7.0 - 56.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E143" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F143" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G143" s="8" t="inlineStr"/>
+      <c r="H143" s="8" t="inlineStr"/>
+      <c r="I143" s="8" t="inlineStr"/>
+      <c r="J143" s="8" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
@@ -4905,10 +5193,12 @@
       </c>
       <c r="D144" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.1 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 18.09 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E144" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4920,34 +5210,36 @@
       <c r="J144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B145" s="7" t="inlineStr">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C145" s="7" t="n">
+      <c r="C145" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D145" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 40.24 U/L outside normal range [10.0 - 40.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E145" s="7" t="n"/>
-      <c r="F145" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="inlineStr"/>
-      <c r="H145" s="7" t="inlineStr"/>
-      <c r="I145" s="7" t="inlineStr"/>
-      <c r="J145" s="7" t="inlineStr"/>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.7 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F145" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G145" s="8" t="inlineStr"/>
+      <c r="H145" s="8" t="inlineStr"/>
+      <c r="I145" s="8" t="inlineStr"/>
+      <c r="J145" s="8" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
@@ -4965,10 +5257,12 @@
       </c>
       <c r="D146" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.7 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 40.24 U/L outside normal range [10.0 - 40.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F146" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -4980,34 +5274,36 @@
       <c r="J146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="A147" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C147" s="7" t="n">
+      <c r="C147" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D147" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 40.78 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E147" s="7" t="n"/>
-      <c r="F147" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="inlineStr"/>
-      <c r="H147" s="7" t="inlineStr"/>
-      <c r="I147" s="7" t="inlineStr"/>
-      <c r="J147" s="7" t="inlineStr"/>
+      <c r="D147" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.32 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F147" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G147" s="8" t="inlineStr"/>
+      <c r="H147" s="8" t="inlineStr"/>
+      <c r="I147" s="8" t="inlineStr"/>
+      <c r="J147" s="8" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
@@ -5025,10 +5321,12 @@
       </c>
       <c r="D148" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 3.32 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 40.78 U/L outside normal range [10.0 - 40.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F148" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5040,34 +5338,36 @@
       <c r="J148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B149" s="7" t="inlineStr">
+      <c r="A149" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C149" s="7" t="n">
+      <c r="C149" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D149" s="7" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>White Blood Cells (WBC) = 12.11 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E149" s="7" t="n"/>
-      <c r="F149" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="inlineStr"/>
-      <c r="H149" s="7" t="inlineStr"/>
-      <c r="I149" s="7" t="inlineStr"/>
-      <c r="J149" s="7" t="inlineStr"/>
+      <c r="E149" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F149" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G149" s="8" t="inlineStr"/>
+      <c r="H149" s="8" t="inlineStr"/>
+      <c r="I149" s="8" t="inlineStr"/>
+      <c r="J149" s="8" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="6" t="inlineStr">
@@ -5085,10 +5385,12 @@
       </c>
       <c r="D150" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 37.55 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 6.72 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E150" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5100,34 +5402,36 @@
       <c r="J150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B151" s="7" t="inlineStr">
+      <c r="A151" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C151" s="7" t="n">
+      <c r="C151" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D151" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 19.95 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E151" s="7" t="n"/>
-      <c r="F151" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G151" s="7" t="inlineStr"/>
-      <c r="H151" s="7" t="inlineStr"/>
-      <c r="I151" s="7" t="inlineStr"/>
-      <c r="J151" s="7" t="inlineStr"/>
+      <c r="D151" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 37.55 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E151" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F151" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G151" s="8" t="inlineStr"/>
+      <c r="H151" s="8" t="inlineStr"/>
+      <c r="I151" s="8" t="inlineStr"/>
+      <c r="J151" s="8" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="6" t="inlineStr">
@@ -5145,10 +5449,12 @@
       </c>
       <c r="D152" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.72 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 19.95 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5160,34 +5466,36 @@
       <c r="J152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
+      <c r="A153" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C153" s="7" t="n">
+      <c r="C153" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D153" s="7" t="inlineStr">
+      <c r="D153" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 400.7 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E153" s="7" t="n"/>
-      <c r="F153" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G153" s="7" t="inlineStr"/>
-      <c r="H153" s="7" t="inlineStr"/>
-      <c r="I153" s="7" t="inlineStr"/>
-      <c r="J153" s="7" t="inlineStr"/>
+      <c r="E153" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F153" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G153" s="8" t="inlineStr"/>
+      <c r="H153" s="8" t="inlineStr"/>
+      <c r="I153" s="8" t="inlineStr"/>
+      <c r="J153" s="8" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="6" t="inlineStr">
@@ -5205,10 +5513,12 @@
       </c>
       <c r="D154" s="6" t="inlineStr">
         <is>
-          <t>Bilirubin (BILI) = 23.83 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 11.89 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E154" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5220,34 +5530,36 @@
       <c r="J154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
+      <c r="A155" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C155" s="7" t="n">
+      <c r="C155" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D155" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 11.89 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E155" s="7" t="n"/>
-      <c r="F155" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G155" s="7" t="inlineStr"/>
-      <c r="H155" s="7" t="inlineStr"/>
-      <c r="I155" s="7" t="inlineStr"/>
-      <c r="J155" s="7" t="inlineStr"/>
+      <c r="D155" s="8" t="inlineStr">
+        <is>
+          <t>Bilirubin (BILI) = 23.83 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E155" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F155" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G155" s="8" t="inlineStr"/>
+      <c r="H155" s="8" t="inlineStr"/>
+      <c r="I155" s="8" t="inlineStr"/>
+      <c r="J155" s="8" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="6" t="inlineStr">
@@ -5265,10 +5577,12 @@
       </c>
       <c r="D156" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.46 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.62 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E156" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F156" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5280,34 +5594,36 @@
       <c r="J156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
+      <c r="A157" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C157" s="7" t="n">
+      <c r="C157" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D157" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.62 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E157" s="7" t="n"/>
-      <c r="F157" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G157" s="7" t="inlineStr"/>
-      <c r="H157" s="7" t="inlineStr"/>
-      <c r="I157" s="7" t="inlineStr"/>
-      <c r="J157" s="7" t="inlineStr"/>
+      <c r="D157" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 11.02 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E157" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F157" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G157" s="8" t="inlineStr"/>
+      <c r="H157" s="8" t="inlineStr"/>
+      <c r="I157" s="8" t="inlineStr"/>
+      <c r="J157" s="8" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="6" t="inlineStr">
@@ -5325,10 +5641,12 @@
       </c>
       <c r="D158" s="6" t="inlineStr">
         <is>
-          <t>Platelets (PLT) = 452.37 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 10.46 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E158" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5340,34 +5658,36 @@
       <c r="J158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
+      <c r="A159" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B159" s="8" t="inlineStr">
         <is>
           <t>SUBJ-012</t>
         </is>
       </c>
-      <c r="C159" s="7" t="n">
+      <c r="C159" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D159" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 11.02 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E159" s="7" t="n"/>
-      <c r="F159" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G159" s="7" t="inlineStr"/>
-      <c r="H159" s="7" t="inlineStr"/>
-      <c r="I159" s="7" t="inlineStr"/>
-      <c r="J159" s="7" t="inlineStr"/>
+      <c r="D159" s="8" t="inlineStr">
+        <is>
+          <t>Platelets (PLT) = 452.37 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F159" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G159" s="8" t="inlineStr"/>
+      <c r="H159" s="8" t="inlineStr"/>
+      <c r="I159" s="8" t="inlineStr"/>
+      <c r="J159" s="8" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="6" t="inlineStr">
@@ -5388,7 +5708,9 @@
           <t>Aspartate Aminotransf (AST) = 44.9 U/L outside normal range [10.0 - 40.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E160" s="6" t="n"/>
+      <c r="E160" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5400,34 +5722,36 @@
       <c r="J160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
+      <c r="A161" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B161" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C161" s="7" t="n">
+      <c r="C161" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D161" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 18.8 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E161" s="7" t="n"/>
-      <c r="F161" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G161" s="7" t="inlineStr"/>
-      <c r="H161" s="7" t="inlineStr"/>
-      <c r="I161" s="7" t="inlineStr"/>
-      <c r="J161" s="7" t="inlineStr"/>
+      <c r="D161" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 11.18 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E161" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F161" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G161" s="8" t="inlineStr"/>
+      <c r="H161" s="8" t="inlineStr"/>
+      <c r="I161" s="8" t="inlineStr"/>
+      <c r="J161" s="8" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="6" t="inlineStr">
@@ -5445,10 +5769,12 @@
       </c>
       <c r="D162" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 11.18 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 18.8 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5460,34 +5786,36 @@
       <c r="J162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B163" s="7" t="inlineStr">
+      <c r="A163" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B163" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C163" s="7" t="n">
+      <c r="C163" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D163" s="7" t="inlineStr">
-        <is>
-          <t>Bilirubin (BILI) = 21.51 umol/L outside normal range [3.0 - 21.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E163" s="7" t="n"/>
-      <c r="F163" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G163" s="7" t="inlineStr"/>
-      <c r="H163" s="7" t="inlineStr"/>
-      <c r="I163" s="7" t="inlineStr"/>
-      <c r="J163" s="7" t="inlineStr"/>
+      <c r="D163" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.57 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F163" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G163" s="8" t="inlineStr"/>
+      <c r="H163" s="8" t="inlineStr"/>
+      <c r="I163" s="8" t="inlineStr"/>
+      <c r="J163" s="8" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="6" t="inlineStr">
@@ -5508,7 +5836,9 @@
           <t>Hemoglobin (HGB) = 11.69 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E164" s="6" t="n"/>
+      <c r="E164" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F164" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5520,34 +5850,36 @@
       <c r="J164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B165" s="7" t="inlineStr">
+      <c r="A165" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B165" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C165" s="7" t="n">
+      <c r="C165" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D165" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.57 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E165" s="7" t="n"/>
-      <c r="F165" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G165" s="7" t="inlineStr"/>
-      <c r="H165" s="7" t="inlineStr"/>
-      <c r="I165" s="7" t="inlineStr"/>
-      <c r="J165" s="7" t="inlineStr"/>
+      <c r="D165" s="8" t="inlineStr">
+        <is>
+          <t>Bilirubin (BILI) = 21.51 umol/L outside normal range [3.0 - 21.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F165" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G165" s="8" t="inlineStr"/>
+      <c r="H165" s="8" t="inlineStr"/>
+      <c r="I165" s="8" t="inlineStr"/>
+      <c r="J165" s="8" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -5565,10 +5897,12 @@
       </c>
       <c r="D166" s="6" t="inlineStr">
         <is>
-          <t>Aspartate Aminotransf (AST) = 40.11 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="n"/>
+          <t>Glucose (GLUC) = 8.35 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E166" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5580,34 +5914,36 @@
       <c r="J166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B167" s="7" t="inlineStr">
+      <c r="A167" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B167" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C167" s="7" t="n">
+      <c r="C167" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D167" s="7" t="inlineStr">
+      <c r="D167" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 41.57 umol/L outside normal range [44.0 - 106.0] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E167" s="7" t="n"/>
-      <c r="F167" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G167" s="7" t="inlineStr"/>
-      <c r="H167" s="7" t="inlineStr"/>
-      <c r="I167" s="7" t="inlineStr"/>
-      <c r="J167" s="7" t="inlineStr"/>
+      <c r="E167" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F167" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G167" s="8" t="inlineStr"/>
+      <c r="H167" s="8" t="inlineStr"/>
+      <c r="I167" s="8" t="inlineStr"/>
+      <c r="J167" s="8" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="6" t="inlineStr">
@@ -5625,10 +5961,12 @@
       </c>
       <c r="D168" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 8.35 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 40.11 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E168" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5640,34 +5978,36 @@
       <c r="J168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B169" s="7" t="inlineStr">
+      <c r="A169" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C169" s="7" t="n">
+      <c r="C169" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D169" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 40.19 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E169" s="7" t="n"/>
-      <c r="F169" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G169" s="7" t="inlineStr"/>
-      <c r="H169" s="7" t="inlineStr"/>
-      <c r="I169" s="7" t="inlineStr"/>
-      <c r="J169" s="7" t="inlineStr"/>
+      <c r="D169" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 8.26 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E169" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F169" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G169" s="8" t="inlineStr"/>
+      <c r="H169" s="8" t="inlineStr"/>
+      <c r="I169" s="8" t="inlineStr"/>
+      <c r="J169" s="8" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="6" t="inlineStr">
@@ -5685,10 +6025,12 @@
       </c>
       <c r="D170" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 8.26 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E170" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 40.19 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E170" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5700,34 +6042,36 @@
       <c r="J170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B171" s="7" t="inlineStr">
+      <c r="A171" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B171" s="8" t="inlineStr">
         <is>
           <t>SUBJ-013</t>
         </is>
       </c>
-      <c r="C171" s="7" t="n">
+      <c r="C171" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D171" s="7" t="inlineStr">
+      <c r="D171" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 11.96 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E171" s="7" t="n"/>
-      <c r="F171" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G171" s="7" t="inlineStr"/>
-      <c r="H171" s="7" t="inlineStr"/>
-      <c r="I171" s="7" t="inlineStr"/>
-      <c r="J171" s="7" t="inlineStr"/>
+      <c r="E171" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F171" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G171" s="8" t="inlineStr"/>
+      <c r="H171" s="8" t="inlineStr"/>
+      <c r="I171" s="8" t="inlineStr"/>
+      <c r="J171" s="8" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="6" t="inlineStr">
@@ -5748,7 +6092,9 @@
           <t>Bilirubin (BILI) = 2.71 umol/L outside normal range [3.0 - 21.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E172" s="6" t="n"/>
+      <c r="E172" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5760,34 +6106,36 @@
       <c r="J172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="A173" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="C173" s="7" t="n">
+      <c r="C173" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D173" s="7" t="inlineStr">
+      <c r="D173" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 19.2 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E173" s="7" t="n"/>
-      <c r="F173" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G173" s="7" t="inlineStr"/>
-      <c r="H173" s="7" t="inlineStr"/>
-      <c r="I173" s="7" t="inlineStr"/>
-      <c r="J173" s="7" t="inlineStr"/>
+      <c r="E173" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F173" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G173" s="8" t="inlineStr"/>
+      <c r="H173" s="8" t="inlineStr"/>
+      <c r="I173" s="8" t="inlineStr"/>
+      <c r="J173" s="8" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="6" t="inlineStr">
@@ -5808,7 +6156,9 @@
           <t>Platelets (PLT) = 139.24 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E174" s="6" t="n"/>
+      <c r="E174" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5820,34 +6170,36 @@
       <c r="J174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B175" s="7" t="inlineStr">
+      <c r="A175" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B175" s="8" t="inlineStr">
         <is>
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="C175" s="7" t="n">
+      <c r="C175" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D175" s="7" t="inlineStr">
-        <is>
-          <t>Bilirubin (BILI) = 2.64 umol/L outside normal range [3.0 - 21.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E175" s="7" t="n"/>
-      <c r="F175" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G175" s="7" t="inlineStr"/>
-      <c r="H175" s="7" t="inlineStr"/>
-      <c r="I175" s="7" t="inlineStr"/>
-      <c r="J175" s="7" t="inlineStr"/>
+      <c r="D175" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.64 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E175" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F175" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G175" s="8" t="inlineStr"/>
+      <c r="H175" s="8" t="inlineStr"/>
+      <c r="I175" s="8" t="inlineStr"/>
+      <c r="J175" s="8" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="6" t="inlineStr">
@@ -5865,10 +6217,12 @@
       </c>
       <c r="D176" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.09 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E176" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 12.33 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E176" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5880,34 +6234,36 @@
       <c r="J176" s="6" t="inlineStr"/>
     </row>
     <row r="177">
-      <c r="A177" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B177" s="7" t="inlineStr">
+      <c r="A177" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="C177" s="7" t="n">
+      <c r="C177" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D177" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 3.64 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E177" s="7" t="n"/>
-      <c r="F177" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G177" s="7" t="inlineStr"/>
-      <c r="H177" s="7" t="inlineStr"/>
-      <c r="I177" s="7" t="inlineStr"/>
-      <c r="J177" s="7" t="inlineStr"/>
+      <c r="D177" s="8" t="inlineStr">
+        <is>
+          <t>Bilirubin (BILI) = 2.64 umol/L outside normal range [3.0 - 21.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E177" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F177" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G177" s="8" t="inlineStr"/>
+      <c r="H177" s="8" t="inlineStr"/>
+      <c r="I177" s="8" t="inlineStr"/>
+      <c r="J177" s="8" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="6" t="inlineStr">
@@ -5925,10 +6281,12 @@
       </c>
       <c r="D178" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.33 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E178" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 10.09 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E178" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -5940,34 +6298,36 @@
       <c r="J178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B179" s="7" t="inlineStr">
+      <c r="A179" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="C179" s="7" t="n">
+      <c r="C179" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D179" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 64.14 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E179" s="7" t="n"/>
-      <c r="F179" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G179" s="7" t="inlineStr"/>
-      <c r="H179" s="7" t="inlineStr"/>
-      <c r="I179" s="7" t="inlineStr"/>
-      <c r="J179" s="7" t="inlineStr"/>
+      <c r="D179" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 7.97 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E179" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F179" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G179" s="8" t="inlineStr"/>
+      <c r="H179" s="8" t="inlineStr"/>
+      <c r="I179" s="8" t="inlineStr"/>
+      <c r="J179" s="8" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="inlineStr">
@@ -5985,10 +6345,12 @@
       </c>
       <c r="D180" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 7.97 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E180" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 64.14 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E180" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6000,34 +6362,36 @@
       <c r="J180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B181" s="7" t="inlineStr">
+      <c r="A181" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>SUBJ-014</t>
         </is>
       </c>
-      <c r="C181" s="7" t="n">
+      <c r="C181" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D181" s="7" t="inlineStr">
+      <c r="D181" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 10.42 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E181" s="7" t="n"/>
-      <c r="F181" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G181" s="7" t="inlineStr"/>
-      <c r="H181" s="7" t="inlineStr"/>
-      <c r="I181" s="7" t="inlineStr"/>
-      <c r="J181" s="7" t="inlineStr"/>
+      <c r="E181" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F181" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G181" s="8" t="inlineStr"/>
+      <c r="H181" s="8" t="inlineStr"/>
+      <c r="I181" s="8" t="inlineStr"/>
+      <c r="J181" s="8" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="6" t="inlineStr">
@@ -6048,7 +6412,9 @@
           <t>Hemoglobin (HGB) = 17.99 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E182" s="6" t="n"/>
+      <c r="E182" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6060,34 +6426,36 @@
       <c r="J182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B183" s="7" t="inlineStr">
+      <c r="A183" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C183" s="7" t="n">
+      <c r="C183" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D183" s="7" t="inlineStr">
-        <is>
-          <t>C-Reactive Protein (CRPROT) = 10.29 mg/L outside normal range [0.0 - 10.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E183" s="7" t="n"/>
-      <c r="F183" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G183" s="7" t="inlineStr"/>
-      <c r="H183" s="7" t="inlineStr"/>
-      <c r="I183" s="7" t="inlineStr"/>
-      <c r="J183" s="7" t="inlineStr"/>
+      <c r="D183" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 3.82 mmol/L outside normal range [3.9 - 7.8] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E183" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F183" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G183" s="8" t="inlineStr"/>
+      <c r="H183" s="8" t="inlineStr"/>
+      <c r="I183" s="8" t="inlineStr"/>
+      <c r="J183" s="8" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="6" t="inlineStr">
@@ -6105,10 +6473,12 @@
       </c>
       <c r="D184" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 3.82 mmol/L outside normal range [3.9 - 7.8] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E184" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 3.86 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E184" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6120,34 +6490,36 @@
       <c r="J184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B185" s="7" t="inlineStr">
+      <c r="A185" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C185" s="7" t="n">
+      <c r="C185" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D185" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 3.86 10^9/L outside normal range [4.0 - 11.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E185" s="7" t="n"/>
-      <c r="F185" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G185" s="7" t="inlineStr"/>
-      <c r="H185" s="7" t="inlineStr"/>
-      <c r="I185" s="7" t="inlineStr"/>
-      <c r="J185" s="7" t="inlineStr"/>
+      <c r="D185" s="8" t="inlineStr">
+        <is>
+          <t>C-Reactive Protein (CRPROT) = 10.29 mg/L outside normal range [0.0 - 10.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E185" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F185" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G185" s="8" t="inlineStr"/>
+      <c r="H185" s="8" t="inlineStr"/>
+      <c r="I185" s="8" t="inlineStr"/>
+      <c r="J185" s="8" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="inlineStr">
@@ -6165,10 +6537,12 @@
       </c>
       <c r="D186" s="6" t="inlineStr">
         <is>
-          <t>Alanine Aminotransf (ALT) = 57.74 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E186" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 6.72 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E186" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F186" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6180,34 +6554,36 @@
       <c r="J186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B187" s="7" t="inlineStr">
+      <c r="A187" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C187" s="7" t="n">
+      <c r="C187" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D187" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.72 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E187" s="7" t="n"/>
-      <c r="F187" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G187" s="7" t="inlineStr"/>
-      <c r="H187" s="7" t="inlineStr"/>
-      <c r="I187" s="7" t="inlineStr"/>
-      <c r="J187" s="7" t="inlineStr"/>
+      <c r="D187" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 57.74 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E187" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F187" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G187" s="8" t="inlineStr"/>
+      <c r="H187" s="8" t="inlineStr"/>
+      <c r="I187" s="8" t="inlineStr"/>
+      <c r="J187" s="8" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -6228,7 +6604,9 @@
           <t>Platelets (PLT) = 137.08 10^9/L outside normal range [150.0 - 400.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E188" s="6" t="n"/>
+      <c r="E188" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F188" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6240,34 +6618,36 @@
       <c r="J188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B189" s="7" t="inlineStr">
+      <c r="A189" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B189" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C189" s="7" t="n">
+      <c r="C189" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D189" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 41.95 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E189" s="7" t="n"/>
-      <c r="F189" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G189" s="7" t="inlineStr"/>
-      <c r="H189" s="7" t="inlineStr"/>
-      <c r="I189" s="7" t="inlineStr"/>
-      <c r="J189" s="7" t="inlineStr"/>
+      <c r="D189" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.53 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E189" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F189" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G189" s="8" t="inlineStr"/>
+      <c r="H189" s="8" t="inlineStr"/>
+      <c r="I189" s="8" t="inlineStr"/>
+      <c r="J189" s="8" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="6" t="inlineStr">
@@ -6285,10 +6665,12 @@
       </c>
       <c r="D190" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.94 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E190" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 41.95 U/L outside normal range [10.0 - 40.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E190" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F190" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6300,34 +6682,36 @@
       <c r="J190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B191" s="7" t="inlineStr">
+      <c r="A191" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B191" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C191" s="7" t="n">
+      <c r="C191" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D191" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.53 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E191" s="7" t="n"/>
-      <c r="F191" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G191" s="7" t="inlineStr"/>
-      <c r="H191" s="7" t="inlineStr"/>
-      <c r="I191" s="7" t="inlineStr"/>
-      <c r="J191" s="7" t="inlineStr"/>
+      <c r="D191" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 12.04 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E191" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F191" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G191" s="8" t="inlineStr"/>
+      <c r="H191" s="8" t="inlineStr"/>
+      <c r="I191" s="8" t="inlineStr"/>
+      <c r="J191" s="8" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="6" t="inlineStr">
@@ -6345,10 +6729,12 @@
       </c>
       <c r="D192" s="6" t="inlineStr">
         <is>
-          <t>White Blood Cells (WBC) = 12.04 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E192" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 10.94 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E192" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F192" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6360,34 +6746,36 @@
       <c r="J192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B193" s="7" t="inlineStr">
+      <c r="A193" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C193" s="7" t="n">
+      <c r="C193" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D193" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 62.25 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E193" s="7" t="n"/>
-      <c r="F193" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G193" s="7" t="inlineStr"/>
-      <c r="H193" s="7" t="inlineStr"/>
-      <c r="I193" s="7" t="inlineStr"/>
-      <c r="J193" s="7" t="inlineStr"/>
+      <c r="D193" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.89 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E193" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F193" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G193" s="8" t="inlineStr"/>
+      <c r="H193" s="8" t="inlineStr"/>
+      <c r="I193" s="8" t="inlineStr"/>
+      <c r="J193" s="8" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="6" t="inlineStr">
@@ -6408,7 +6796,9 @@
           <t>Glucose (GLUC) = 8.86 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E194" s="6" t="n"/>
+      <c r="E194" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6420,34 +6810,36 @@
       <c r="J194" s="6" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B195" s="7" t="inlineStr">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C195" s="7" t="n">
+      <c r="C195" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D195" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.89 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E195" s="7" t="n"/>
-      <c r="F195" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G195" s="7" t="inlineStr"/>
-      <c r="H195" s="7" t="inlineStr"/>
-      <c r="I195" s="7" t="inlineStr"/>
-      <c r="J195" s="7" t="inlineStr"/>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 62.25 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E195" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F195" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G195" s="8" t="inlineStr"/>
+      <c r="H195" s="8" t="inlineStr"/>
+      <c r="I195" s="8" t="inlineStr"/>
+      <c r="J195" s="8" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="6" t="inlineStr">
@@ -6468,7 +6860,9 @@
           <t>White Blood Cells (WBC) = 11.03 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E196" s="6" t="n"/>
+      <c r="E196" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F196" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6480,34 +6874,36 @@
       <c r="J196" s="6" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B197" s="7" t="inlineStr">
+      <c r="A197" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B197" s="8" t="inlineStr">
         <is>
           <t>SUBJ-015</t>
         </is>
       </c>
-      <c r="C197" s="7" t="n">
+      <c r="C197" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D197" s="7" t="inlineStr">
+      <c r="D197" s="8" t="inlineStr">
         <is>
           <t>White Blood Cells (WBC) = 11.15 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E197" s="7" t="n"/>
-      <c r="F197" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G197" s="7" t="inlineStr"/>
-      <c r="H197" s="7" t="inlineStr"/>
-      <c r="I197" s="7" t="inlineStr"/>
-      <c r="J197" s="7" t="inlineStr"/>
+      <c r="E197" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F197" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G197" s="8" t="inlineStr"/>
+      <c r="H197" s="8" t="inlineStr"/>
+      <c r="I197" s="8" t="inlineStr"/>
+      <c r="J197" s="8" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="6" t="inlineStr">
@@ -6525,10 +6921,12 @@
       </c>
       <c r="D198" s="6" t="inlineStr">
         <is>
-          <t>Aspartate Aminotransf (AST) = 40.78 U/L outside normal range [10.0 - 40.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E198" s="6" t="n"/>
+          <t>Creatinine (CREAT) = 118.82 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E198" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6540,34 +6938,36 @@
       <c r="J198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="A199" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C199" s="7" t="n">
+      <c r="C199" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D199" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 118.82 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E199" s="7" t="n"/>
-      <c r="F199" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G199" s="7" t="inlineStr"/>
-      <c r="H199" s="7" t="inlineStr"/>
-      <c r="I199" s="7" t="inlineStr"/>
-      <c r="J199" s="7" t="inlineStr"/>
+      <c r="D199" s="8" t="inlineStr">
+        <is>
+          <t>Aspartate Aminotransf (AST) = 40.78 U/L outside normal range [10.0 - 40.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E199" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F199" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G199" s="8" t="inlineStr"/>
+      <c r="H199" s="8" t="inlineStr"/>
+      <c r="I199" s="8" t="inlineStr"/>
+      <c r="J199" s="8" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="6" t="inlineStr">
@@ -6588,7 +6988,9 @@
           <t>Hemoglobin (HGB) = 19.34 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E200" s="6" t="n"/>
+      <c r="E200" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6600,34 +7002,36 @@
       <c r="J200" s="6" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B201" s="7" t="inlineStr">
+      <c r="A201" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C201" s="7" t="n">
+      <c r="C201" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D201" s="7" t="inlineStr">
+      <c r="D201" s="8" t="inlineStr">
         <is>
           <t>Platelets (PLT) = 451.75 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E201" s="7" t="n"/>
-      <c r="F201" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G201" s="7" t="inlineStr"/>
-      <c r="H201" s="7" t="inlineStr"/>
-      <c r="I201" s="7" t="inlineStr"/>
-      <c r="J201" s="7" t="inlineStr"/>
+      <c r="E201" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F201" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G201" s="8" t="inlineStr"/>
+      <c r="H201" s="8" t="inlineStr"/>
+      <c r="I201" s="8" t="inlineStr"/>
+      <c r="J201" s="8" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="6" t="inlineStr">
@@ -6648,7 +7052,9 @@
           <t>Creatinine (CREAT) = 41.88 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E202" s="6" t="n"/>
+      <c r="E202" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6660,34 +7066,36 @@
       <c r="J202" s="6" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B203" s="7" t="inlineStr">
+      <c r="A203" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B203" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C203" s="7" t="n">
+      <c r="C203" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D203" s="7" t="inlineStr">
+      <c r="D203" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 11.22 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E203" s="7" t="n"/>
-      <c r="F203" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G203" s="7" t="inlineStr"/>
-      <c r="H203" s="7" t="inlineStr"/>
-      <c r="I203" s="7" t="inlineStr"/>
-      <c r="J203" s="7" t="inlineStr"/>
+      <c r="E203" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F203" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G203" s="8" t="inlineStr"/>
+      <c r="H203" s="8" t="inlineStr"/>
+      <c r="I203" s="8" t="inlineStr"/>
+      <c r="J203" s="8" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="6" t="inlineStr">
@@ -6705,10 +7113,12 @@
       </c>
       <c r="D204" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.68 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E204" s="6" t="n"/>
+          <t>Glucose (GLUC) = 8.01 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6720,34 +7130,36 @@
       <c r="J204" s="6" t="inlineStr"/>
     </row>
     <row r="205">
-      <c r="A205" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B205" s="7" t="inlineStr">
+      <c r="A205" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B205" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C205" s="7" t="n">
+      <c r="C205" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D205" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 8.01 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E205" s="7" t="n"/>
-      <c r="F205" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G205" s="7" t="inlineStr"/>
-      <c r="H205" s="7" t="inlineStr"/>
-      <c r="I205" s="7" t="inlineStr"/>
-      <c r="J205" s="7" t="inlineStr"/>
+      <c r="D205" s="8" t="inlineStr">
+        <is>
+          <t>Platelets (PLT) = 408.8 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E205" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F205" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G205" s="8" t="inlineStr"/>
+      <c r="H205" s="8" t="inlineStr"/>
+      <c r="I205" s="8" t="inlineStr"/>
+      <c r="J205" s="8" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="6" t="inlineStr">
@@ -6765,10 +7177,12 @@
       </c>
       <c r="D206" s="6" t="inlineStr">
         <is>
-          <t>Platelets (PLT) = 408.8 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E206" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 10.68 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E206" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F206" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6780,34 +7194,36 @@
       <c r="J206" s="6" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B207" s="7" t="inlineStr">
+      <c r="A207" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C207" s="7" t="n">
+      <c r="C207" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D207" s="7" t="inlineStr">
-        <is>
-          <t>Aspartate Aminotransf (AST) = 41.63 U/L outside normal range [10.0 - 40.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E207" s="7" t="n"/>
-      <c r="F207" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G207" s="7" t="inlineStr"/>
-      <c r="H207" s="7" t="inlineStr"/>
-      <c r="I207" s="7" t="inlineStr"/>
-      <c r="J207" s="7" t="inlineStr"/>
+      <c r="D207" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 43.16 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E207" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F207" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G207" s="8" t="inlineStr"/>
+      <c r="H207" s="8" t="inlineStr"/>
+      <c r="I207" s="8" t="inlineStr"/>
+      <c r="J207" s="8" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="6" t="inlineStr">
@@ -6825,10 +7241,12 @@
       </c>
       <c r="D208" s="6" t="inlineStr">
         <is>
-          <t>Bilirubin (BILI) = 21.68 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E208" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 41.63 U/L outside normal range [10.0 - 40.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E208" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6840,34 +7258,36 @@
       <c r="J208" s="6" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B209" s="7" t="inlineStr">
+      <c r="A209" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C209" s="7" t="n">
+      <c r="C209" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D209" s="7" t="inlineStr">
-        <is>
-          <t>Creatinine (CREAT) = 43.16 umol/L outside normal range [44.0 - 106.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E209" s="7" t="n"/>
-      <c r="F209" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G209" s="7" t="inlineStr"/>
-      <c r="H209" s="7" t="inlineStr"/>
-      <c r="I209" s="7" t="inlineStr"/>
-      <c r="J209" s="7" t="inlineStr"/>
+      <c r="D209" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 10.29 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E209" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F209" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G209" s="8" t="inlineStr"/>
+      <c r="H209" s="8" t="inlineStr"/>
+      <c r="I209" s="8" t="inlineStr"/>
+      <c r="J209" s="8" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -6885,10 +7305,12 @@
       </c>
       <c r="D210" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.29 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E210" s="6" t="n"/>
+          <t>Platelets (PLT) = 428.25 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6900,34 +7322,36 @@
       <c r="J210" s="6" t="inlineStr"/>
     </row>
     <row r="211">
-      <c r="A211" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B211" s="7" t="inlineStr">
+      <c r="A211" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B211" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C211" s="7" t="n">
+      <c r="C211" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D211" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 428.25 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E211" s="7" t="n"/>
-      <c r="F211" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G211" s="7" t="inlineStr"/>
-      <c r="H211" s="7" t="inlineStr"/>
-      <c r="I211" s="7" t="inlineStr"/>
-      <c r="J211" s="7" t="inlineStr"/>
+      <c r="D211" s="8" t="inlineStr">
+        <is>
+          <t>Bilirubin (BILI) = 21.68 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E211" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F211" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G211" s="8" t="inlineStr"/>
+      <c r="H211" s="8" t="inlineStr"/>
+      <c r="I211" s="8" t="inlineStr"/>
+      <c r="J211" s="8" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="6" t="inlineStr">
@@ -6945,10 +7369,12 @@
       </c>
       <c r="D212" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 18.92 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E212" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 11.13 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -6960,34 +7386,36 @@
       <c r="J212" s="6" t="inlineStr"/>
     </row>
     <row r="213">
-      <c r="A213" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B213" s="7" t="inlineStr">
+      <c r="A213" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B213" s="8" t="inlineStr">
         <is>
           <t>SUBJ-016</t>
         </is>
       </c>
-      <c r="C213" s="7" t="n">
+      <c r="C213" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D213" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 11.13 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E213" s="7" t="n"/>
-      <c r="F213" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G213" s="7" t="inlineStr"/>
-      <c r="H213" s="7" t="inlineStr"/>
-      <c r="I213" s="7" t="inlineStr"/>
-      <c r="J213" s="7" t="inlineStr"/>
+      <c r="D213" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 18.92 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E213" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F213" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G213" s="8" t="inlineStr"/>
+      <c r="H213" s="8" t="inlineStr"/>
+      <c r="I213" s="8" t="inlineStr"/>
+      <c r="J213" s="8" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="6" t="inlineStr">
@@ -7005,10 +7433,12 @@
       </c>
       <c r="D214" s="6" t="inlineStr">
         <is>
-          <t>Creatinine (CREAT) = 38.83 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E214" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 6.75 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E214" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7020,34 +7450,36 @@
       <c r="J214" s="6" t="inlineStr"/>
     </row>
     <row r="215">
-      <c r="A215" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B215" s="7" t="inlineStr">
+      <c r="A215" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B215" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C215" s="7" t="n">
+      <c r="C215" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D215" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.75 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E215" s="7" t="n"/>
-      <c r="F215" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G215" s="7" t="inlineStr"/>
-      <c r="H215" s="7" t="inlineStr"/>
-      <c r="I215" s="7" t="inlineStr"/>
-      <c r="J215" s="7" t="inlineStr"/>
+      <c r="D215" s="8" t="inlineStr">
+        <is>
+          <t>Creatinine (CREAT) = 38.83 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E215" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F215" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G215" s="8" t="inlineStr"/>
+      <c r="H215" s="8" t="inlineStr"/>
+      <c r="I215" s="8" t="inlineStr"/>
+      <c r="J215" s="8" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="6" t="inlineStr">
@@ -7068,7 +7500,9 @@
           <t>Platelets (PLT) = 400.86 10^9/L outside normal range [150.0 - 400.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E216" s="6" t="n"/>
+      <c r="E216" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7080,34 +7514,36 @@
       <c r="J216" s="6" t="inlineStr"/>
     </row>
     <row r="217">
-      <c r="A217" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B217" s="7" t="inlineStr">
+      <c r="A217" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B217" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C217" s="7" t="n">
+      <c r="C217" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D217" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 61.3 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E217" s="7" t="n"/>
-      <c r="F217" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G217" s="7" t="inlineStr"/>
-      <c r="H217" s="7" t="inlineStr"/>
-      <c r="I217" s="7" t="inlineStr"/>
-      <c r="J217" s="7" t="inlineStr"/>
+      <c r="D217" s="8" t="inlineStr">
+        <is>
+          <t>Glucose (GLUC) = 8.26 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E217" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F217" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G217" s="8" t="inlineStr"/>
+      <c r="H217" s="8" t="inlineStr"/>
+      <c r="I217" s="8" t="inlineStr"/>
+      <c r="J217" s="8" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="6" t="inlineStr">
@@ -7128,7 +7564,9 @@
           <t>Creatinine (CREAT) = 37.83 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E218" s="6" t="n"/>
+      <c r="E218" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7140,34 +7578,36 @@
       <c r="J218" s="6" t="inlineStr"/>
     </row>
     <row r="219">
-      <c r="A219" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B219" s="7" t="inlineStr">
+      <c r="A219" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C219" s="7" t="n">
+      <c r="C219" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D219" s="7" t="inlineStr">
-        <is>
-          <t>Glucose (GLUC) = 8.26 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E219" s="7" t="n"/>
-      <c r="F219" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G219" s="7" t="inlineStr"/>
-      <c r="H219" s="7" t="inlineStr"/>
-      <c r="I219" s="7" t="inlineStr"/>
-      <c r="J219" s="7" t="inlineStr"/>
+      <c r="D219" s="8" t="inlineStr">
+        <is>
+          <t>Alanine Aminotransf (ALT) = 61.3 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E219" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F219" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G219" s="8" t="inlineStr"/>
+      <c r="H219" s="8" t="inlineStr"/>
+      <c r="I219" s="8" t="inlineStr"/>
+      <c r="J219" s="8" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="6" t="inlineStr">
@@ -7188,7 +7628,9 @@
           <t>White Blood Cells (WBC) = 11.78 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E220" s="6" t="n"/>
+      <c r="E220" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7200,34 +7642,36 @@
       <c r="J220" s="6" t="inlineStr"/>
     </row>
     <row r="221">
-      <c r="A221" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B221" s="7" t="inlineStr">
+      <c r="A221" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B221" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C221" s="7" t="n">
+      <c r="C221" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D221" s="7" t="inlineStr">
+      <c r="D221" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 8.36 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E221" s="7" t="n"/>
-      <c r="F221" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G221" s="7" t="inlineStr"/>
-      <c r="H221" s="7" t="inlineStr"/>
-      <c r="I221" s="7" t="inlineStr"/>
-      <c r="J221" s="7" t="inlineStr"/>
+      <c r="E221" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F221" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G221" s="8" t="inlineStr"/>
+      <c r="H221" s="8" t="inlineStr"/>
+      <c r="I221" s="8" t="inlineStr"/>
+      <c r="J221" s="8" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="6" t="inlineStr">
@@ -7245,10 +7689,12 @@
       </c>
       <c r="D222" s="6" t="inlineStr">
         <is>
-          <t>Platelets (PLT) = 131.02 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E222" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 11.33 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E222" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7260,34 +7706,36 @@
       <c r="J222" s="6" t="inlineStr"/>
     </row>
     <row r="223">
-      <c r="A223" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B223" s="7" t="inlineStr">
+      <c r="A223" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B223" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C223" s="7" t="n">
+      <c r="C223" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D223" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 11.33 10^9/L outside normal range [4.0 - 11.0] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E223" s="7" t="n"/>
-      <c r="F223" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G223" s="7" t="inlineStr"/>
-      <c r="H223" s="7" t="inlineStr"/>
-      <c r="I223" s="7" t="inlineStr"/>
-      <c r="J223" s="7" t="inlineStr"/>
+      <c r="D223" s="8" t="inlineStr">
+        <is>
+          <t>Platelets (PLT) = 131.02 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E223" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F223" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G223" s="8" t="inlineStr"/>
+      <c r="H223" s="8" t="inlineStr"/>
+      <c r="I223" s="8" t="inlineStr"/>
+      <c r="J223" s="8" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="6" t="inlineStr">
@@ -7305,10 +7753,12 @@
       </c>
       <c r="D224" s="6" t="inlineStr">
         <is>
-          <t>Aspartate Aminotransf (AST) = 45.27 U/L outside normal range [10.0 - 40.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E224" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 7.23 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E224" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F224" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7320,34 +7770,36 @@
       <c r="J224" s="6" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="A225" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C225" s="7" t="n">
+      <c r="C225" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D225" s="7" t="inlineStr">
+      <c r="D225" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 41.02 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E225" s="7" t="n"/>
-      <c r="F225" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G225" s="7" t="inlineStr"/>
-      <c r="H225" s="7" t="inlineStr"/>
-      <c r="I225" s="7" t="inlineStr"/>
-      <c r="J225" s="7" t="inlineStr"/>
+      <c r="E225" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F225" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G225" s="8" t="inlineStr"/>
+      <c r="H225" s="8" t="inlineStr"/>
+      <c r="I225" s="8" t="inlineStr"/>
+      <c r="J225" s="8" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="6" t="inlineStr">
@@ -7365,10 +7817,12 @@
       </c>
       <c r="D226" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.23 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E226" s="6" t="n"/>
+          <t>Aspartate Aminotransf (AST) = 45.27 U/L outside normal range [10.0 - 40.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E226" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7380,34 +7834,36 @@
       <c r="J226" s="6" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B227" s="7" t="inlineStr">
+      <c r="A227" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B227" s="8" t="inlineStr">
         <is>
           <t>SUBJ-017</t>
         </is>
       </c>
-      <c r="C227" s="7" t="n">
+      <c r="C227" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D227" s="7" t="inlineStr">
+      <c r="D227" s="8" t="inlineStr">
         <is>
           <t>White Blood Cells (WBC) = 12.36 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E227" s="7" t="n"/>
-      <c r="F227" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G227" s="7" t="inlineStr"/>
-      <c r="H227" s="7" t="inlineStr"/>
-      <c r="I227" s="7" t="inlineStr"/>
-      <c r="J227" s="7" t="inlineStr"/>
+      <c r="E227" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F227" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G227" s="8" t="inlineStr"/>
+      <c r="H227" s="8" t="inlineStr"/>
+      <c r="I227" s="8" t="inlineStr"/>
+      <c r="J227" s="8" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="6" t="inlineStr">
@@ -7425,10 +7881,12 @@
       </c>
       <c r="D228" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 10.42 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E228" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 3.43 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E228" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F228" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7440,34 +7898,36 @@
       <c r="J228" s="6" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B229" s="7" t="inlineStr">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
         <is>
           <t>SUBJ-018</t>
         </is>
       </c>
-      <c r="C229" s="7" t="n">
+      <c r="C229" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D229" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.43 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E229" s="7" t="n"/>
-      <c r="F229" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G229" s="7" t="inlineStr"/>
-      <c r="H229" s="7" t="inlineStr"/>
-      <c r="I229" s="7" t="inlineStr"/>
-      <c r="J229" s="7" t="inlineStr"/>
+      <c r="D229" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 10.42 g/dL outside normal range [12.0 - 17.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E229" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F229" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G229" s="8" t="inlineStr"/>
+      <c r="H229" s="8" t="inlineStr"/>
+      <c r="I229" s="8" t="inlineStr"/>
+      <c r="J229" s="8" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="6" t="inlineStr">
@@ -7488,7 +7948,9 @@
           <t>Hemoglobin A1C (HBA1C) = 7.35 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E230" s="6" t="n"/>
+      <c r="E230" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7500,34 +7962,36 @@
       <c r="J230" s="6" t="inlineStr"/>
     </row>
     <row r="231">
-      <c r="A231" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B231" s="7" t="inlineStr">
+      <c r="A231" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B231" s="8" t="inlineStr">
         <is>
           <t>SUBJ-018</t>
         </is>
       </c>
-      <c r="C231" s="7" t="n">
+      <c r="C231" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D231" s="7" t="inlineStr">
+      <c r="D231" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 18.19 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E231" s="7" t="n"/>
-      <c r="F231" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G231" s="7" t="inlineStr"/>
-      <c r="H231" s="7" t="inlineStr"/>
-      <c r="I231" s="7" t="inlineStr"/>
-      <c r="J231" s="7" t="inlineStr"/>
+      <c r="E231" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F231" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G231" s="8" t="inlineStr"/>
+      <c r="H231" s="8" t="inlineStr"/>
+      <c r="I231" s="8" t="inlineStr"/>
+      <c r="J231" s="8" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="6" t="inlineStr">
@@ -7548,7 +8012,9 @@
           <t>Bilirubin (BILI) = 21.02 umol/L outside normal range [3.0 - 21.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E232" s="6" t="n"/>
+      <c r="E232" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7560,34 +8026,36 @@
       <c r="J232" s="6" t="inlineStr"/>
     </row>
     <row r="233">
-      <c r="A233" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B233" s="7" t="inlineStr">
+      <c r="A233" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="inlineStr">
         <is>
           <t>SUBJ-018</t>
         </is>
       </c>
-      <c r="C233" s="7" t="n">
+      <c r="C233" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D233" s="7" t="inlineStr">
+      <c r="D233" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 118.91 umol/L outside normal range [44.0 - 106.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E233" s="7" t="n"/>
-      <c r="F233" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G233" s="7" t="inlineStr"/>
-      <c r="H233" s="7" t="inlineStr"/>
-      <c r="I233" s="7" t="inlineStr"/>
-      <c r="J233" s="7" t="inlineStr"/>
+      <c r="E233" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F233" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G233" s="8" t="inlineStr"/>
+      <c r="H233" s="8" t="inlineStr"/>
+      <c r="I233" s="8" t="inlineStr"/>
+      <c r="J233" s="8" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="6" t="inlineStr">
@@ -7605,10 +8073,12 @@
       </c>
       <c r="D234" s="6" t="inlineStr">
         <is>
-          <t>Platelets (PLT) = 146.61 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E234" s="6" t="n"/>
+          <t>White Blood Cells (WBC) = 3.75 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E234" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F234" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7620,34 +8090,36 @@
       <c r="J234" s="6" t="inlineStr"/>
     </row>
     <row r="235">
-      <c r="A235" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B235" s="7" t="inlineStr">
+      <c r="A235" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>SUBJ-018</t>
         </is>
       </c>
-      <c r="C235" s="7" t="n">
+      <c r="C235" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D235" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 3.75 10^9/L outside normal range [4.0 - 11.0] at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E235" s="7" t="n"/>
-      <c r="F235" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G235" s="7" t="inlineStr"/>
-      <c r="H235" s="7" t="inlineStr"/>
-      <c r="I235" s="7" t="inlineStr"/>
-      <c r="J235" s="7" t="inlineStr"/>
+      <c r="D235" s="8" t="inlineStr">
+        <is>
+          <t>Platelets (PLT) = 146.61 10^9/L outside normal range [150.0 - 400.0] at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E235" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F235" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G235" s="8" t="inlineStr"/>
+      <c r="H235" s="8" t="inlineStr"/>
+      <c r="I235" s="8" t="inlineStr"/>
+      <c r="J235" s="8" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="inlineStr">
@@ -7668,7 +8140,9 @@
           <t>Creatinine (CREAT) = 121.63 umol/L outside normal range [44.0 - 106.0] at visit SCREENING</t>
         </is>
       </c>
-      <c r="E236" s="6" t="n"/>
+      <c r="E236" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F236" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7680,34 +8154,36 @@
       <c r="J236" s="6" t="inlineStr"/>
     </row>
     <row r="237">
-      <c r="A237" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B237" s="7" t="inlineStr">
+      <c r="A237" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B237" s="8" t="inlineStr">
         <is>
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="C237" s="7" t="n">
+      <c r="C237" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D237" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 58.35 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E237" s="7" t="n"/>
-      <c r="F237" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G237" s="7" t="inlineStr"/>
-      <c r="H237" s="7" t="inlineStr"/>
-      <c r="I237" s="7" t="inlineStr"/>
-      <c r="J237" s="7" t="inlineStr"/>
+      <c r="D237" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 6.71 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E237" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F237" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G237" s="8" t="inlineStr"/>
+      <c r="H237" s="8" t="inlineStr"/>
+      <c r="I237" s="8" t="inlineStr"/>
+      <c r="J237" s="8" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="6" t="inlineStr">
@@ -7725,10 +8201,12 @@
       </c>
       <c r="D238" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.71 mg/L outside normal range [0.0 - 10.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E238" s="6" t="n"/>
+          <t>Glucose (GLUC) = 8.78 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7740,34 +8218,36 @@
       <c r="J238" s="6" t="inlineStr"/>
     </row>
     <row r="239">
-      <c r="A239" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B239" s="7" t="inlineStr">
+      <c r="A239" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="C239" s="7" t="n">
+      <c r="C239" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D239" s="7" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>Creatinine (CREAT) = 118.62 umol/L outside normal range [44.0 - 106.0] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E239" s="7" t="n"/>
-      <c r="F239" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G239" s="7" t="inlineStr"/>
-      <c r="H239" s="7" t="inlineStr"/>
-      <c r="I239" s="7" t="inlineStr"/>
-      <c r="J239" s="7" t="inlineStr"/>
+      <c r="E239" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F239" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G239" s="8" t="inlineStr"/>
+      <c r="H239" s="8" t="inlineStr"/>
+      <c r="I239" s="8" t="inlineStr"/>
+      <c r="J239" s="8" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="6" t="inlineStr">
@@ -7785,10 +8265,12 @@
       </c>
       <c r="D240" s="6" t="inlineStr">
         <is>
-          <t>Glucose (GLUC) = 8.78 mmol/L outside normal range [3.9 - 7.8] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E240" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 58.35 U/L outside normal range [7.0 - 56.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E240" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7800,34 +8282,36 @@
       <c r="J240" s="6" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B241" s="7" t="inlineStr">
+      <c r="A241" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="C241" s="7" t="n">
+      <c r="C241" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D241" s="7" t="inlineStr">
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>Hemoglobin (HGB) = 19.68 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
         </is>
       </c>
-      <c r="E241" s="7" t="n"/>
-      <c r="F241" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G241" s="7" t="inlineStr"/>
-      <c r="H241" s="7" t="inlineStr"/>
-      <c r="I241" s="7" t="inlineStr"/>
-      <c r="J241" s="7" t="inlineStr"/>
+      <c r="E241" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F241" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G241" s="8" t="inlineStr"/>
+      <c r="H241" s="8" t="inlineStr"/>
+      <c r="I241" s="8" t="inlineStr"/>
+      <c r="J241" s="8" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="6" t="inlineStr">
@@ -7845,10 +8329,12 @@
       </c>
       <c r="D242" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.71 % outside normal range [4.0 - 6.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E242" s="6" t="n"/>
+          <t>C-Reactive Protein (CRPROT) = 10.71 mg/L outside normal range [0.0 - 10.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E242" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7860,34 +8346,36 @@
       <c r="J242" s="6" t="inlineStr"/>
     </row>
     <row r="243">
-      <c r="A243" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B243" s="7" t="inlineStr">
+      <c r="A243" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B243" s="8" t="inlineStr">
         <is>
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="C243" s="7" t="n">
+      <c r="C243" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D243" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 17.79 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E243" s="7" t="n"/>
-      <c r="F243" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G243" s="7" t="inlineStr"/>
-      <c r="H243" s="7" t="inlineStr"/>
-      <c r="I243" s="7" t="inlineStr"/>
-      <c r="J243" s="7" t="inlineStr"/>
+      <c r="D243" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 7.04 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E243" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F243" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G243" s="8" t="inlineStr"/>
+      <c r="H243" s="8" t="inlineStr"/>
+      <c r="I243" s="8" t="inlineStr"/>
+      <c r="J243" s="8" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="inlineStr">
@@ -7905,10 +8393,12 @@
       </c>
       <c r="D244" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 7.04 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E244" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 17.79 g/dL outside normal range [12.0 - 17.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F244" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7920,34 +8410,36 @@
       <c r="J244" s="6" t="inlineStr"/>
     </row>
     <row r="245">
-      <c r="A245" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B245" s="7" t="inlineStr">
+      <c r="A245" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B245" s="8" t="inlineStr">
         <is>
           <t>SUBJ-019</t>
         </is>
       </c>
-      <c r="C245" s="7" t="n">
+      <c r="C245" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D245" s="7" t="inlineStr">
+      <c r="D245" s="8" t="inlineStr">
         <is>
           <t>Alanine Aminotransf (ALT) = 6.44 U/L outside normal range [7.0 - 56.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E245" s="7" t="n"/>
-      <c r="F245" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G245" s="7" t="inlineStr"/>
-      <c r="H245" s="7" t="inlineStr"/>
-      <c r="I245" s="7" t="inlineStr"/>
-      <c r="J245" s="7" t="inlineStr"/>
+      <c r="E245" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F245" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G245" s="8" t="inlineStr"/>
+      <c r="H245" s="8" t="inlineStr"/>
+      <c r="I245" s="8" t="inlineStr"/>
+      <c r="J245" s="8" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="6" t="inlineStr">
@@ -7968,7 +8460,9 @@
           <t>Hemoglobin A1C (HBA1C) = 6.72 % outside normal range [4.0 - 6.5] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E246" s="6" t="n"/>
+      <c r="E246" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F246" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -7980,34 +8474,36 @@
       <c r="J246" s="6" t="inlineStr"/>
     </row>
     <row r="247">
-      <c r="A247" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B247" s="7" t="inlineStr">
+      <c r="A247" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B247" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C247" s="7" t="n">
+      <c r="C247" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="D247" s="7" t="inlineStr">
-        <is>
-          <t>Alanine Aminotransf (ALT) = 57.95 U/L outside normal range [7.0 - 56.0] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E247" s="7" t="n"/>
-      <c r="F247" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G247" s="7" t="inlineStr"/>
-      <c r="H247" s="7" t="inlineStr"/>
-      <c r="I247" s="7" t="inlineStr"/>
-      <c r="J247" s="7" t="inlineStr"/>
+      <c r="D247" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin A1C (HBA1C) = 3.89 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E247" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F247" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G247" s="8" t="inlineStr"/>
+      <c r="H247" s="8" t="inlineStr"/>
+      <c r="I247" s="8" t="inlineStr"/>
+      <c r="J247" s="8" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="6" t="inlineStr">
@@ -8025,10 +8521,12 @@
       </c>
       <c r="D248" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 3.89 % outside normal range [4.0 - 6.5] at visit SCREENING</t>
-        </is>
-      </c>
-      <c r="E248" s="6" t="n"/>
+          <t>Alanine Aminotransf (ALT) = 57.95 U/L outside normal range [7.0 - 56.0] at visit SCREENING</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8040,34 +8538,36 @@
       <c r="J248" s="6" t="inlineStr"/>
     </row>
     <row r="249">
-      <c r="A249" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B249" s="7" t="inlineStr">
+      <c r="A249" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B249" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C249" s="7" t="n">
+      <c r="C249" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D249" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin (HGB) = 11.23 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E249" s="7" t="n"/>
-      <c r="F249" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G249" s="7" t="inlineStr"/>
-      <c r="H249" s="7" t="inlineStr"/>
-      <c r="I249" s="7" t="inlineStr"/>
-      <c r="J249" s="7" t="inlineStr"/>
+      <c r="D249" s="8" t="inlineStr">
+        <is>
+          <t>White Blood Cells (WBC) = 3.9 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E249" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F249" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G249" s="8" t="inlineStr"/>
+      <c r="H249" s="8" t="inlineStr"/>
+      <c r="I249" s="8" t="inlineStr"/>
+      <c r="J249" s="8" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="6" t="inlineStr">
@@ -8085,10 +8585,12 @@
       </c>
       <c r="D250" s="6" t="inlineStr">
         <is>
-          <t>Platelets (PLT) = 437.25 10^9/L outside normal range [150.0 - 400.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E250" s="6" t="n"/>
+          <t>Hemoglobin (HGB) = 11.23 g/dL outside normal range [12.0 - 17.5] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E250" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8100,34 +8602,36 @@
       <c r="J250" s="6" t="inlineStr"/>
     </row>
     <row r="251">
-      <c r="A251" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="A251" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C251" s="7" t="n">
+      <c r="C251" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D251" s="7" t="inlineStr">
-        <is>
-          <t>White Blood Cells (WBC) = 3.9 10^9/L outside normal range [4.0 - 11.0] at visit BASELINE</t>
-        </is>
-      </c>
-      <c r="E251" s="7" t="n"/>
-      <c r="F251" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G251" s="7" t="inlineStr"/>
-      <c r="H251" s="7" t="inlineStr"/>
-      <c r="I251" s="7" t="inlineStr"/>
-      <c r="J251" s="7" t="inlineStr"/>
+      <c r="D251" s="8" t="inlineStr">
+        <is>
+          <t>Platelets (PLT) = 437.25 10^9/L outside normal range [150.0 - 400.0] at visit BASELINE</t>
+        </is>
+      </c>
+      <c r="E251" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F251" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G251" s="8" t="inlineStr"/>
+      <c r="H251" s="8" t="inlineStr"/>
+      <c r="I251" s="8" t="inlineStr"/>
+      <c r="J251" s="8" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="6" t="inlineStr">
@@ -8145,10 +8649,12 @@
       </c>
       <c r="D252" s="6" t="inlineStr">
         <is>
-          <t>C-Reactive Protein (CRPROT) = 10.89 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E252" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 6.91 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E252" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8160,34 +8666,36 @@
       <c r="J252" s="6" t="inlineStr"/>
     </row>
     <row r="253">
-      <c r="A253" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B253" s="7" t="inlineStr">
+      <c r="A253" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B253" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C253" s="7" t="n">
+      <c r="C253" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D253" s="7" t="inlineStr">
+      <c r="D253" s="8" t="inlineStr">
         <is>
           <t>Glucose (GLUC) = 8.83 mmol/L outside normal range [3.9 - 7.8] at visit WEEK 4</t>
         </is>
       </c>
-      <c r="E253" s="7" t="n"/>
-      <c r="F253" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G253" s="7" t="inlineStr"/>
-      <c r="H253" s="7" t="inlineStr"/>
-      <c r="I253" s="7" t="inlineStr"/>
-      <c r="J253" s="7" t="inlineStr"/>
+      <c r="E253" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F253" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G253" s="8" t="inlineStr"/>
+      <c r="H253" s="8" t="inlineStr"/>
+      <c r="I253" s="8" t="inlineStr"/>
+      <c r="J253" s="8" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="6" t="inlineStr">
@@ -8205,10 +8713,12 @@
       </c>
       <c r="D254" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.91 % outside normal range [4.0 - 6.5] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E254" s="6" t="n"/>
+          <t>Platelets (PLT) = 131.01 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E254" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F254" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8220,34 +8730,36 @@
       <c r="J254" s="6" t="inlineStr"/>
     </row>
     <row r="255">
-      <c r="A255" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B255" s="7" t="inlineStr">
+      <c r="A255" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B255" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C255" s="7" t="n">
+      <c r="C255" s="8" t="n">
         <v>300</v>
       </c>
-      <c r="D255" s="7" t="inlineStr">
-        <is>
-          <t>Platelets (PLT) = 131.01 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 4</t>
-        </is>
-      </c>
-      <c r="E255" s="7" t="n"/>
-      <c r="F255" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G255" s="7" t="inlineStr"/>
-      <c r="H255" s="7" t="inlineStr"/>
-      <c r="I255" s="7" t="inlineStr"/>
-      <c r="J255" s="7" t="inlineStr"/>
+      <c r="D255" s="8" t="inlineStr">
+        <is>
+          <t>C-Reactive Protein (CRPROT) = 10.89 mg/L outside normal range [0.0 - 10.0] at visit WEEK 4</t>
+        </is>
+      </c>
+      <c r="E255" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F255" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G255" s="8" t="inlineStr"/>
+      <c r="H255" s="8" t="inlineStr"/>
+      <c r="I255" s="8" t="inlineStr"/>
+      <c r="J255" s="8" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="6" t="inlineStr">
@@ -8265,10 +8777,12 @@
       </c>
       <c r="D256" s="6" t="inlineStr">
         <is>
-          <t>Hemoglobin (HGB) = 17.57 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E256" s="6" t="n"/>
+          <t>Hemoglobin A1C (HBA1C) = 6.65 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E256" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F256" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8280,34 +8794,36 @@
       <c r="J256" s="6" t="inlineStr"/>
     </row>
     <row r="257">
-      <c r="A257" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B257" s="7" t="inlineStr">
+      <c r="A257" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B257" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C257" s="7" t="n">
+      <c r="C257" s="8" t="n">
         <v>400</v>
       </c>
-      <c r="D257" s="7" t="inlineStr">
-        <is>
-          <t>Hemoglobin A1C (HBA1C) = 6.65 % outside normal range [4.0 - 6.5] at visit WEEK 8</t>
-        </is>
-      </c>
-      <c r="E257" s="7" t="n"/>
-      <c r="F257" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G257" s="7" t="inlineStr"/>
-      <c r="H257" s="7" t="inlineStr"/>
-      <c r="I257" s="7" t="inlineStr"/>
-      <c r="J257" s="7" t="inlineStr"/>
+      <c r="D257" s="8" t="inlineStr">
+        <is>
+          <t>Hemoglobin (HGB) = 17.57 g/dL outside normal range [12.0 - 17.5] at visit WEEK 8</t>
+        </is>
+      </c>
+      <c r="E257" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F257" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G257" s="8" t="inlineStr"/>
+      <c r="H257" s="8" t="inlineStr"/>
+      <c r="I257" s="8" t="inlineStr"/>
+      <c r="J257" s="8" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="6" t="inlineStr">
@@ -8328,7 +8844,9 @@
           <t>Platelets (PLT) = 411.28 10^9/L outside normal range [150.0 - 400.0] at visit WEEK 8</t>
         </is>
       </c>
-      <c r="E258" s="6" t="n"/>
+      <c r="E258" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8340,34 +8858,36 @@
       <c r="J258" s="6" t="inlineStr"/>
     </row>
     <row r="259">
-      <c r="A259" s="7" t="inlineStr">
-        <is>
-          <t>LBCHK001</t>
-        </is>
-      </c>
-      <c r="B259" s="7" t="inlineStr">
+      <c r="A259" s="8" t="inlineStr">
+        <is>
+          <t>LBCHK001</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="inlineStr">
         <is>
           <t>SUBJ-020</t>
         </is>
       </c>
-      <c r="C259" s="7" t="n">
+      <c r="C259" s="8" t="n">
         <v>500</v>
       </c>
-      <c r="D259" s="7" t="inlineStr">
+      <c r="D259" s="8" t="inlineStr">
         <is>
           <t>Alanine Aminotransf (ALT) = 6.81 U/L outside normal range [7.0 - 56.0] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E259" s="7" t="n"/>
-      <c r="F259" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G259" s="7" t="inlineStr"/>
-      <c r="H259" s="7" t="inlineStr"/>
-      <c r="I259" s="7" t="inlineStr"/>
-      <c r="J259" s="7" t="inlineStr"/>
+      <c r="E259" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F259" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G259" s="8" t="inlineStr"/>
+      <c r="H259" s="8" t="inlineStr"/>
+      <c r="I259" s="8" t="inlineStr"/>
+      <c r="J259" s="8" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="6" t="inlineStr">
@@ -8388,7 +8908,9 @@
           <t>Hemoglobin (HGB) = 18.57 g/dL outside normal range [12.0 - 17.5] at visit END OF TREATMENT</t>
         </is>
       </c>
-      <c r="E260" s="6" t="n"/>
+      <c r="E260" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8400,34 +8922,36 @@
       <c r="J260" s="6" t="inlineStr"/>
     </row>
     <row r="261">
-      <c r="A261" s="7" t="inlineStr">
+      <c r="A261" s="8" t="inlineStr">
         <is>
           <t>LBCHK003</t>
         </is>
       </c>
-      <c r="B261" s="7" t="inlineStr">
+      <c r="B261" s="8" t="inlineStr">
         <is>
           <t>SUBJ-001</t>
         </is>
       </c>
-      <c r="C261" s="7" t="n">
+      <c r="C261" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D261" s="7" t="inlineStr">
+      <c r="D261" s="8" t="inlineStr">
         <is>
           <t>Duplicate records for test Glucose (GLUC) at visit BASELINE - more than one result recorded</t>
         </is>
       </c>
-      <c r="E261" s="7" t="n"/>
-      <c r="F261" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G261" s="7" t="inlineStr"/>
-      <c r="H261" s="7" t="inlineStr"/>
-      <c r="I261" s="7" t="inlineStr"/>
-      <c r="J261" s="7" t="inlineStr"/>
+      <c r="E261" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F261" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G261" s="8" t="inlineStr"/>
+      <c r="H261" s="8" t="inlineStr"/>
+      <c r="I261" s="8" t="inlineStr"/>
+      <c r="J261" s="8" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="6" t="inlineStr">
@@ -8448,7 +8972,9 @@
           <t>Duplicate records for test Glucose (GLUC) at visit BASELINE - more than one result recorded</t>
         </is>
       </c>
-      <c r="E262" s="6" t="n"/>
+      <c r="E262" s="7" t="n">
+        <v>46135</v>
+      </c>
       <c r="F262" s="6" t="inlineStr">
         <is>
           <t>open</t>
@@ -8460,34 +8986,36 @@
       <c r="J262" s="6" t="inlineStr"/>
     </row>
     <row r="263">
-      <c r="A263" s="7" t="inlineStr">
+      <c r="A263" s="8" t="inlineStr">
         <is>
           <t>LBCHK003</t>
         </is>
       </c>
-      <c r="B263" s="7" t="inlineStr">
+      <c r="B263" s="8" t="inlineStr">
         <is>
           <t>SUBJ-003</t>
         </is>
       </c>
-      <c r="C263" s="7" t="n">
+      <c r="C263" s="8" t="n">
         <v>200</v>
       </c>
-      <c r="D263" s="7" t="inlineStr">
+      <c r="D263" s="8" t="inlineStr">
         <is>
           <t>Duplicate records for test Glucose (GLUC) at visit BASELINE - more than one result recorded</t>
         </is>
       </c>
-      <c r="E263" s="7" t="n"/>
-      <c r="F263" s="7" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="G263" s="7" t="inlineStr"/>
-      <c r="H263" s="7" t="inlineStr"/>
-      <c r="I263" s="7" t="inlineStr"/>
-      <c r="J263" s="7" t="inlineStr"/>
+      <c r="E263" s="9" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F263" s="8" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="G263" s="8" t="inlineStr"/>
+      <c r="H263" s="8" t="inlineStr"/>
+      <c r="I263" s="8" t="inlineStr"/>
+      <c r="J263" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
